--- a/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
+++ b/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\fonlar\etki-analizi\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C21A6472-563A-4D27-B657-DE9B2F3079A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D41969A-0F3C-4E39-81B8-98537440F74F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19245" yWindow="0" windowWidth="14400" windowHeight="20550" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20790" yWindow="420" windowWidth="12765" windowHeight="20415" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TLY" sheetId="1" r:id="rId1"/>
@@ -466,7 +466,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -527,7 +527,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -893,13 +892,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="19">
-        <v>18.96129386379215</v>
+        <v>19.695279429999999</v>
       </c>
       <c r="C2" s="4">
-        <v>3.87096774193548</v>
+        <v>3.1055900621118</v>
       </c>
       <c r="D2" s="5">
-        <v>0.73398556892098565</v>
+        <v>0.6116546406832295</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -907,13 +906,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="19">
-        <v>20.622154475748985</v>
+        <v>21.275529670000001</v>
       </c>
       <c r="C3" s="4">
-        <v>3.16831683168316</v>
+        <v>4.4145873320537401</v>
       </c>
       <c r="D3" s="5">
-        <v>0.65337519131085731</v>
+        <v>0.93922683763915504</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -921,13 +920,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="19">
-        <v>11.127283266791489</v>
+        <v>11.20146516</v>
       </c>
       <c r="C4" s="4">
-        <v>0.66666666666666596</v>
+        <v>-1.0347682119205199</v>
       </c>
       <c r="D4" s="5">
-        <v>7.4181888445276511E-2</v>
+        <v>-0.11590920074503201</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -935,13 +934,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="19">
-        <v>9.958469483779723</v>
+        <v>9.709507747</v>
       </c>
       <c r="C5" s="4">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="D5" s="5">
-        <v>-0.24896173709449307</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -949,13 +948,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="19">
-        <v>0.32049104872903883</v>
+        <v>0.33639089599999999</v>
       </c>
       <c r="C6" s="4">
-        <v>4.9610894941634198</v>
+        <v>3.7998146431881299</v>
       </c>
       <c r="D6" s="5">
-        <v>1.589984774823051E-2</v>
+        <v>1.2782230524559752E-2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -963,13 +962,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="19">
-        <v>7.1042028014805192</v>
+        <v>7.5373858990000002</v>
       </c>
       <c r="C7" s="4">
-        <v>6.09756097560975</v>
+        <v>3.44827586206896</v>
       </c>
       <c r="D7" s="5">
-        <v>0.43318309765125074</v>
+        <v>0.25990985858620652</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -977,13 +976,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="19">
-        <v>2.7271180235266761</v>
+        <v>2.4554804940000001</v>
       </c>
       <c r="C8" s="4">
-        <v>-9.9606077658975796</v>
+        <v>-10</v>
       </c>
       <c r="D8" s="5">
-        <v>-0.27163752963659066</v>
+        <v>-0.2455480494</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -991,13 +990,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="19">
-        <v>2.0266666666666664</v>
+        <v>1.8240000000000001</v>
       </c>
       <c r="C9" s="4">
-        <v>-10</v>
+        <v>-9.9537037037037006</v>
       </c>
       <c r="D9" s="5">
-        <v>-0.20266666666666666</v>
+        <v>-0.18155555555555553</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1005,13 +1004,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="19">
-        <v>1.9142833875004066</v>
+        <v>1.992715832</v>
       </c>
       <c r="C10" s="4">
-        <v>4.0972222222222197</v>
+        <v>4.6697798532354904</v>
       </c>
       <c r="D10" s="5">
-        <v>7.843244434897495E-2</v>
+        <v>9.305544245496998E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1019,13 +1018,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="19">
-        <v>0.34848795753369671</v>
+        <v>0.31376696900000001</v>
       </c>
       <c r="C11" s="4">
-        <v>-9.9633251833740797</v>
+        <v>-9.9796334012219905</v>
       </c>
       <c r="D11" s="5">
-        <v>-3.4720988433980776E-2</v>
+        <v>-3.1312793240325848E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1033,13 +1032,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="19">
-        <v>0.16679508216279068</v>
+        <v>0.164156359</v>
       </c>
       <c r="C12" s="4">
-        <v>-1.5820149875103999</v>
+        <v>-3.4686971235194499</v>
       </c>
       <c r="D12" s="5">
-        <v>-2.6387231982456343E-3</v>
+        <v>-5.6940869027072615E-3</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1047,13 +1046,13 @@
         <v>15</v>
       </c>
       <c r="B13" s="19">
-        <v>0.10532404205603449</v>
+        <v>0.104643557</v>
       </c>
       <c r="C13" s="4">
-        <v>-0.64608758076094697</v>
+        <v>-3.4682080924855399</v>
       </c>
       <c r="D13" s="5">
-        <v>-6.804855552794756E-4</v>
+        <v>-3.6292563121387185E-3</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1061,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="B14" s="19">
-        <v>9.6197464611377667E-2</v>
+        <v>9.5998982999999996E-2</v>
       </c>
       <c r="C14" s="4">
-        <v>-0.20632737276478599</v>
+        <v>-4.1350792556857296</v>
       </c>
       <c r="D14" s="5">
-        <v>-1.9848170139899029E-4</v>
+        <v>-3.9696340317022698E-3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1075,13 +1074,13 @@
         <v>17</v>
       </c>
       <c r="B15" s="19">
-        <v>8.617421613793104E-2</v>
+        <v>8.5617454999999995E-2</v>
       </c>
       <c r="C15" s="4">
-        <v>-0.64608758076094697</v>
+        <v>-3.4682080924855399</v>
       </c>
       <c r="D15" s="5">
-        <v>-5.5676090828526818E-4</v>
+        <v>-2.9693915028901653E-3</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1089,13 +1088,13 @@
         <v>18</v>
       </c>
       <c r="B16" s="19">
-        <v>8.9129500367366873E-2</v>
+        <v>9.0113498E-2</v>
       </c>
       <c r="C16" s="4">
-        <v>1.1040092969203901</v>
+        <v>-10</v>
       </c>
       <c r="D16" s="5">
-        <v>9.8399797035442346E-4</v>
+        <v>-9.0113498000000004E-3</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1103,13 +1102,13 @@
         <v>19</v>
       </c>
       <c r="B17" s="19">
-        <v>0.69881081123076927</v>
+        <v>0.72555955000000005</v>
       </c>
       <c r="C17" s="4">
-        <v>3.8277511961722399</v>
+        <v>7.3732718894009199</v>
       </c>
       <c r="D17" s="5">
-        <v>2.6748739185866705E-2</v>
+        <v>5.3497478341013815E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1117,13 +1116,13 @@
         <v>20</v>
       </c>
       <c r="B18" s="19">
-        <v>7.01138215015773E-2</v>
+        <v>6.9771245999999995E-2</v>
       </c>
       <c r="C18" s="4">
-        <v>-0.488599348534202</v>
+        <v>-2.9459901800327302</v>
       </c>
       <c r="D18" s="5">
-        <v>-3.4257567508913999E-4</v>
+        <v>-2.0554540556464791E-3</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1131,13 +1130,13 @@
         <v>21</v>
       </c>
       <c r="B19" s="19">
-        <v>6.105675117437722E-2</v>
+        <v>6.0064433E-2</v>
       </c>
       <c r="C19" s="4">
-        <v>-1.6252390057361299</v>
+        <v>-3.79008746355685</v>
       </c>
       <c r="D19" s="5">
-        <v>-9.9231813572123119E-4</v>
+        <v>-2.2764945451895034E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1145,13 +1144,13 @@
         <v>35</v>
       </c>
       <c r="B20" s="19">
-        <v>5.9999999764243618E-2</v>
+        <v>5.9247830000000001E-2</v>
       </c>
       <c r="C20" s="4">
-        <v>-1.25361620057859</v>
+        <v>-2.9296875</v>
       </c>
       <c r="D20" s="5">
-        <v>-7.5216971739167386E-4</v>
+        <v>-1.73577626953125E-3</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1159,13 +1158,13 @@
         <v>57</v>
       </c>
       <c r="B21" s="19">
-        <v>5.108974376755749E-2</v>
+        <v>4.8332519999999997E-2</v>
       </c>
       <c r="C21" s="4">
-        <v>-5.3968253968253901</v>
+        <v>1.20805369127516</v>
       </c>
       <c r="D21" s="5">
-        <v>-2.7572242668205595E-3</v>
+        <v>5.8388279194630495E-4</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1173,13 +1172,13 @@
         <v>79</v>
       </c>
       <c r="B22" s="19">
-        <v>3.9584905384972176E-2</v>
+        <v>3.8551935000000002E-2</v>
       </c>
       <c r="C22" s="4">
-        <v>-2.6095060577819198</v>
+        <v>-3.4449760765550201</v>
       </c>
       <c r="D22" s="5">
-        <v>-1.0329705039880902E-3</v>
+        <v>-1.3281049377990416E-3</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1187,13 +1186,13 @@
         <v>74</v>
       </c>
       <c r="B23" s="19">
-        <v>2.801762129550827E-2</v>
+        <v>2.7197708000000001E-2</v>
       </c>
       <c r="C23" s="4">
-        <v>-2.9264214046822699</v>
+        <v>-0.68906115417743297</v>
       </c>
       <c r="D23" s="5">
-        <v>-8.199136666745718E-4</v>
+        <v>-1.8740884065460804E-4</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1201,13 +1200,13 @@
         <v>33</v>
       </c>
       <c r="B24" s="19">
-        <v>2.0320512521052634E-2</v>
+        <v>2.0623803999999999E-2</v>
       </c>
       <c r="C24" s="4">
-        <v>1.4925373134328299</v>
+        <v>1.9607843137254899</v>
       </c>
       <c r="D24" s="5">
-        <v>3.0329123165750082E-4</v>
+        <v>4.0438831372549013E-4</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1215,13 +1214,13 @@
         <v>75</v>
       </c>
       <c r="B25" s="19">
-        <v>1.9888059701492537E-2</v>
+        <v>1.9415717999999998E-2</v>
       </c>
       <c r="C25" s="4">
-        <v>-2.375</v>
+        <v>-4.6734955185659404</v>
       </c>
       <c r="D25" s="5">
-        <v>-4.7234141791044777E-4</v>
+        <v>-9.0739271062740059E-4</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1229,76 +1228,76 @@
         <v>23</v>
       </c>
       <c r="B26" s="7">
-        <v>76.702953507226397</v>
+        <v>77.950816693000007</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="7">
-        <v>1.2478631802349183</v>
+        <v>1.3630248104850062</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="24"/>
-      <c r="B29" s="24"/>
+      <c r="A29" s="23"/>
+      <c r="B29" s="23"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="24"/>
-      <c r="B30" s="24"/>
+      <c r="A30" s="23"/>
+      <c r="B30" s="23"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B31" s="24"/>
-      <c r="C31" s="24"/>
+      <c r="B31" s="23"/>
+      <c r="C31" s="23"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B32" s="24"/>
-      <c r="C32" s="24"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="23"/>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="24"/>
-      <c r="C33" s="24"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="24"/>
-      <c r="C34" s="24"/>
+      <c r="B34" s="23"/>
+      <c r="C34" s="23"/>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="24"/>
-      <c r="C35" s="24"/>
+      <c r="B35" s="23"/>
+      <c r="C35" s="23"/>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="24"/>
-      <c r="C36" s="24"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="23"/>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B37" s="24"/>
-      <c r="C37" s="24"/>
+      <c r="B37" s="23"/>
+      <c r="C37" s="23"/>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B38" s="24"/>
-      <c r="C38" s="24"/>
+      <c r="B38" s="23"/>
+      <c r="C38" s="23"/>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B39" s="24"/>
-      <c r="C39" s="24"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="23"/>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B40" s="24"/>
-      <c r="C40" s="24"/>
+      <c r="B40" s="23"/>
+      <c r="C40" s="23"/>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B41" s="24"/>
-      <c r="C41" s="24"/>
+      <c r="B41" s="23"/>
+      <c r="C41" s="23"/>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B42" s="24"/>
-      <c r="C42" s="24"/>
+      <c r="B42" s="23"/>
+      <c r="C42" s="23"/>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B43" s="24"/>
-      <c r="C43" s="24"/>
+      <c r="B43" s="23"/>
+      <c r="C43" s="23"/>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B44" s="24"/>
-      <c r="C44" s="24"/>
+      <c r="B44" s="23"/>
+      <c r="C44" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -1350,13 +1349,13 @@
         <v>8</v>
       </c>
       <c r="B2" s="19">
-        <v>8.7693297438977513</v>
+        <v>9.2043840410000008</v>
       </c>
       <c r="C2" s="14">
-        <v>4.9610894941634198</v>
+        <v>3.7998146431881299</v>
       </c>
       <c r="D2" s="5">
-        <v>0.43505429663305928</v>
+        <v>0.34974953260518937</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1364,13 +1363,13 @@
         <v>19</v>
       </c>
       <c r="B3" s="19">
-        <v>9.7177081444307696</v>
+        <v>10.089677829999999</v>
       </c>
       <c r="C3" s="14">
-        <v>3.8277511961722399</v>
+        <v>7.3732718894009199</v>
       </c>
       <c r="D3" s="5">
-        <v>0.37196968973897598</v>
+        <v>0.74393937917050668</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1378,13 +1377,13 @@
         <v>9</v>
       </c>
       <c r="B4" s="19">
-        <v>8.018283561545454</v>
+        <v>8.5072032909999997</v>
       </c>
       <c r="C4" s="14">
-        <v>6.09756097560975</v>
+        <v>3.44827586206896</v>
       </c>
       <c r="D4" s="5">
-        <v>0.4889197293625272</v>
+        <v>0.29335183762068917</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1392,13 +1391,13 @@
         <v>6</v>
       </c>
       <c r="B5" s="19">
-        <v>6.3948357915319143</v>
+        <v>6.4374680299999998</v>
       </c>
       <c r="C5" s="14">
-        <v>0.66666666666666596</v>
+        <v>-1.0347682119205199</v>
       </c>
       <c r="D5" s="5">
-        <v>4.2632238610212723E-2</v>
+        <v>-6.6612872826986122E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1406,13 +1405,13 @@
         <v>10</v>
       </c>
       <c r="B6" s="19">
-        <v>5.4852938549849526</v>
+        <v>4.9389252490000004</v>
       </c>
       <c r="C6" s="14">
-        <v>-9.9606077658975796</v>
+        <v>-10</v>
       </c>
       <c r="D6" s="5">
-        <v>-0.54636860570193391</v>
+        <v>-0.49389252490000002</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1420,13 +1419,13 @@
         <v>11</v>
       </c>
       <c r="B7" s="19">
-        <v>6.1506849312820506</v>
+        <v>5.5356164379999999</v>
       </c>
       <c r="C7" s="14">
-        <v>-10</v>
+        <v>-9.9537037037037006</v>
       </c>
       <c r="D7" s="5">
-        <v>-0.61506849312820511</v>
+        <v>-0.55099885841203688</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1434,13 +1433,13 @@
         <v>33</v>
       </c>
       <c r="B8" s="19">
-        <v>4.4884098909126324</v>
+        <v>4.5554010829999996</v>
       </c>
       <c r="C8" s="14">
-        <v>1.4925373134328299</v>
+        <v>1.9607843137254899</v>
       </c>
       <c r="D8" s="5">
-        <v>6.6991192401680819E-2</v>
+        <v>8.9321589862745063E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1448,13 +1447,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="19">
-        <v>3.2680205017327935</v>
+        <v>3.3715617450000002</v>
       </c>
       <c r="C9" s="14">
-        <v>3.16831683168316</v>
+        <v>4.4145873320537401</v>
       </c>
       <c r="D9" s="5">
-        <v>0.10354124361925654</v>
+        <v>0.14884053768714003</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1462,13 +1461,13 @@
         <v>22</v>
       </c>
       <c r="B10" s="19">
-        <v>3.1251202426120224</v>
+        <v>3.1200110539999999</v>
       </c>
       <c r="C10" s="14">
-        <v>-0.163487738419618</v>
+        <v>-5.3493449781659299</v>
       </c>
       <c r="D10" s="5">
-        <v>-5.1091884075400752E-3</v>
+        <v>-0.16690015463537089</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1476,13 +1475,13 @@
         <v>14</v>
       </c>
       <c r="B11" s="19">
-        <v>2.9577093510872094</v>
+        <v>2.9109179460000001</v>
       </c>
       <c r="C11" s="14">
-        <v>-1.5820149875103999</v>
+        <v>-3.4686971235194499</v>
       </c>
       <c r="D11" s="5">
-        <v>-4.679140522119625E-2</v>
+        <v>-0.10097092706091346</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1490,13 +1489,13 @@
         <v>57</v>
       </c>
       <c r="B12" s="19">
-        <v>2.7808700641864514</v>
+        <v>2.6307913620000001</v>
       </c>
       <c r="C12" s="14">
-        <v>-5.3968253968253901</v>
+        <v>1.20805369127516</v>
       </c>
       <c r="D12" s="5">
-        <v>-0.15007870187672895</v>
+        <v>3.1781372158389061E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1504,13 +1503,13 @@
         <v>37</v>
       </c>
       <c r="B13" s="19">
-        <v>2.5430584546504607</v>
+        <v>2.5082043540000001</v>
       </c>
       <c r="C13" s="14">
-        <v>-1.3705583756345101</v>
+        <v>-1.54400411734431</v>
       </c>
       <c r="D13" s="5">
-        <v>-3.4854100647493426E-2</v>
+        <v>-3.8726778497169254E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1518,13 +1517,13 @@
         <v>67</v>
       </c>
       <c r="B14" s="19">
-        <v>2.50830233142571</v>
+        <v>2.5604982180000002</v>
       </c>
       <c r="C14" s="14">
-        <v>2.08092485549132</v>
+        <v>-9.9660249150622793</v>
       </c>
       <c r="D14" s="5">
-        <v>5.219588666550587E-2</v>
+        <v>-0.25517989035560568</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1532,13 +1531,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="19">
-        <v>2.2593822447519618</v>
+        <v>2.2716763439999998</v>
       </c>
       <c r="C15" s="14">
-        <v>0.544135429262394</v>
+        <v>-0.78171978352375204</v>
       </c>
       <c r="D15" s="5">
-        <v>1.22940992761594E-2</v>
+        <v>-1.7758143398677085E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1546,13 +1545,13 @@
         <v>16</v>
       </c>
       <c r="B16" s="19">
-        <v>2.0798950038985606</v>
+        <v>2.075603611</v>
       </c>
       <c r="C16" s="14">
-        <v>-0.20632737276478599</v>
+        <v>-4.1350792556857296</v>
       </c>
       <c r="D16" s="5">
-        <v>-4.2913927178099432E-3</v>
+        <v>-8.5827854348724933E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1560,13 +1559,13 @@
         <v>4</v>
       </c>
       <c r="B17" s="19">
-        <v>1.970285869950249</v>
+        <v>2.0465550000000001</v>
       </c>
       <c r="C17" s="14">
-        <v>3.87096774193548</v>
+        <v>3.1055900621118</v>
       </c>
       <c r="D17" s="5">
-        <v>7.6269130449686987E-2</v>
+        <v>6.3557608695652149E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1574,13 +1573,13 @@
         <v>12</v>
       </c>
       <c r="B18" s="19">
-        <v>4.2210999999999999</v>
+        <v>4.3940478470000004</v>
       </c>
       <c r="C18" s="14">
-        <v>4.0972222222222197</v>
+        <v>4.6697798532354904</v>
       </c>
       <c r="D18" s="5">
-        <v>0.17294784722222212</v>
+        <v>0.20519236110073383</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1588,13 +1587,13 @@
         <v>66</v>
       </c>
       <c r="B19" s="19">
-        <v>2.1022215413390914</v>
+        <v>2.1330773779999999</v>
       </c>
       <c r="C19" s="14">
-        <v>1.4677728142948301</v>
+        <v>-2.2012578616352201</v>
       </c>
       <c r="D19" s="5">
-        <v>3.0855836280024938E-2</v>
+        <v>-4.6954533477987413E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1602,13 +1601,13 @@
         <v>32</v>
       </c>
       <c r="B20" s="19">
-        <v>0.49137328974099098</v>
+        <v>0.492810054</v>
       </c>
       <c r="C20" s="14">
-        <v>0.29239766081871299</v>
+        <v>-2.5072886297375998</v>
       </c>
       <c r="D20" s="5">
-        <v>1.4367640050906147E-3</v>
+        <v>-1.2356170450145724E-2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1616,13 +1615,13 @@
         <v>15</v>
       </c>
       <c r="B21" s="19">
-        <v>1.5690690346584932</v>
+        <v>1.5181388259999999</v>
       </c>
       <c r="C21" s="14">
-        <v>-3.24588706091596</v>
+        <v>-2.5735294117646998</v>
       </c>
       <c r="D21" s="5">
-        <v>-5.0930208772818987E-2</v>
+        <v>-3.9069749198529319E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1630,13 +1629,13 @@
         <v>41</v>
       </c>
       <c r="B22" s="19">
-        <v>1.452385890067948</v>
+        <v>1.45238589</v>
       </c>
       <c r="C22" s="14">
-        <v>0</v>
+        <v>-2.97117516629711</v>
       </c>
       <c r="D22" s="5">
-        <v>0</v>
+        <v>-4.315292888248326E-2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1644,13 +1643,13 @@
         <v>43</v>
       </c>
       <c r="B23" s="19">
-        <v>1.4239377991345028</v>
+        <v>1.407561286</v>
       </c>
       <c r="C23" s="14">
-        <v>-1.15008625646923</v>
+        <v>-3.2577079697498501</v>
       </c>
       <c r="D23" s="5">
-        <v>-1.6376512928516346E-2</v>
+        <v>-4.5854236193135472E-2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1658,13 +1657,13 @@
         <v>20</v>
       </c>
       <c r="B24" s="19">
-        <v>1.2235300000000002</v>
+        <v>1.2175518400000001</v>
       </c>
       <c r="C24" s="14">
-        <v>-0.488599348534202</v>
+        <v>-2.9459901800327302</v>
       </c>
       <c r="D24" s="5">
-        <v>-5.9781596091205225E-3</v>
+        <v>-3.586895764320782E-2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1672,13 +1671,13 @@
         <v>7</v>
       </c>
       <c r="B25" s="19">
-        <v>1.4299117928470046</v>
+        <v>1.394163998</v>
       </c>
       <c r="C25" s="14">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="D25" s="5">
-        <v>-3.5747794821175113E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1686,13 +1685,13 @@
         <v>40</v>
       </c>
       <c r="B26" s="19">
-        <v>1.2669231260052058</v>
+        <v>1.2622702079999999</v>
       </c>
       <c r="C26" s="14">
-        <v>-0.36726128016789</v>
+        <v>-4.8973143759873601</v>
       </c>
       <c r="D26" s="5">
-        <v>-4.6529180913097686E-3</v>
+        <v>-6.1817340360189543E-2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1700,13 +1699,13 @@
         <v>17</v>
       </c>
       <c r="B27" s="19">
-        <v>1.1318390807887933</v>
+        <v>1.124526409</v>
       </c>
       <c r="C27" s="14">
-        <v>-0.64608758076094697</v>
+        <v>-3.4682080924855399</v>
       </c>
       <c r="D27" s="5">
-        <v>-7.3126717351752546E-3</v>
+        <v>-3.9000915919075042E-2</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1714,13 +1713,13 @@
         <v>49</v>
       </c>
       <c r="B28" s="19">
-        <v>1.0214343070454206</v>
+        <v>1.0191509219999999</v>
       </c>
       <c r="C28" s="14">
-        <v>-0.22354694485842</v>
+        <v>-4.5556385362210596</v>
       </c>
       <c r="D28" s="5">
-        <v>-2.2833851871358109E-3</v>
+        <v>-4.6428832144884226E-2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1728,13 +1727,13 @@
         <v>31</v>
       </c>
       <c r="B29" s="19">
-        <v>0.95815277978835989</v>
+        <v>0.93987738600000004</v>
       </c>
       <c r="C29" s="14">
-        <v>-1.9073569482288799</v>
+        <v>-2.9166666666666599</v>
       </c>
       <c r="D29" s="5">
-        <v>-1.8275393619941439E-2</v>
+        <v>-2.7413090424999936E-2</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1742,13 +1741,13 @@
         <v>81</v>
       </c>
       <c r="B30" s="19">
-        <v>0.78393565285989719</v>
+        <v>0.77079706599999998</v>
       </c>
       <c r="C30" s="14">
-        <v>-1.67597765363128</v>
+        <v>-2.6278409090908998</v>
       </c>
       <c r="D30" s="5">
-        <v>-1.3138586360780363E-2</v>
+        <v>-2.0255320626420385E-2</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1756,13 +1755,13 @@
         <v>35</v>
       </c>
       <c r="B31" s="19">
-        <v>0.67604429281799994</v>
+        <v>0.66756929200000004</v>
       </c>
       <c r="C31" s="15">
-        <v>-1.25361620057859</v>
+        <v>-2.9296875</v>
       </c>
       <c r="D31" s="5">
-        <v>-8.4750007778534083E-3</v>
+        <v>-1.9557694101562502E-2</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1770,13 +1769,13 @@
         <v>74</v>
       </c>
       <c r="B32" s="19">
-        <v>0.5682340606713947</v>
+        <v>0.55160513700000002</v>
       </c>
       <c r="C32" s="14">
-        <v>-2.9264214046822699</v>
+        <v>-0.68906115417743297</v>
       </c>
       <c r="D32" s="5">
-        <v>-1.6628923180182931E-2</v>
+        <v>-3.8008967235142106E-3</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1784,13 +1783,13 @@
         <v>82</v>
       </c>
       <c r="B33" s="19">
-        <v>0.61931858435718123</v>
+        <v>0.626728179</v>
       </c>
       <c r="C33" s="14">
-        <v>1.1964107676969</v>
+        <v>-1.5270935960591101</v>
       </c>
       <c r="D33" s="5">
-        <v>7.4095942295973249E-3</v>
+        <v>-9.5707258862068774E-3</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1798,13 +1797,13 @@
         <v>55</v>
       </c>
       <c r="B34" s="19">
-        <v>0.59031751369743901</v>
+        <v>0.58247986399999996</v>
       </c>
       <c r="C34" s="15">
-        <v>-1.3277006638503299</v>
+        <v>-4.0978593272171198</v>
       </c>
       <c r="D34" s="5">
-        <v>-7.8376495481856604E-3</v>
+        <v>-2.3869205436085596E-2</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1812,13 +1811,13 @@
         <v>68</v>
       </c>
       <c r="B35" s="19">
-        <v>0.56041862628515626</v>
+        <v>0.53393117899999998</v>
       </c>
       <c r="C35" s="14">
-        <v>-4.7263681592039797</v>
+        <v>-3.7075718015665799</v>
       </c>
       <c r="D35" s="5">
-        <v>-2.648744751098997E-2</v>
+        <v>-1.9795881832375982E-2</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1826,13 +1825,13 @@
         <v>21</v>
       </c>
       <c r="B36" s="19">
-        <v>0.54646893822064058</v>
+        <v>0.53758751199999999</v>
       </c>
       <c r="C36" s="15">
-        <v>-1.6252390057361299</v>
+        <v>-3.79008746355685</v>
       </c>
       <c r="D36" s="5">
-        <v>-8.8814263381939255E-3</v>
+        <v>-2.0375036897959178E-2</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1840,13 +1839,13 @@
         <v>79</v>
       </c>
       <c r="B37" s="19">
-        <v>0.50170009787940639</v>
+        <v>0.48860820300000002</v>
       </c>
       <c r="C37" s="16">
-        <v>-2.6095060577819198</v>
+        <v>-3.4449760765550201</v>
       </c>
       <c r="D37" s="5">
-        <v>-1.3091894446060929E-2</v>
+        <v>-1.6832435701435389E-2</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1854,13 +1853,13 @@
         <v>78</v>
       </c>
       <c r="B38" s="19">
-        <v>0.48984</v>
+        <v>0.47146307900000001</v>
       </c>
       <c r="C38" s="15">
-        <v>-3.7516170763260002</v>
+        <v>-3.4946236559139701</v>
       </c>
       <c r="D38" s="5">
-        <v>-1.8376921086675279E-2</v>
+        <v>-1.647586028763437E-2</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1868,13 +1867,13 @@
         <v>69</v>
       </c>
       <c r="B39" s="19">
-        <v>0.45675000043269232</v>
+        <v>0.43446951299999997</v>
       </c>
       <c r="C39" s="15">
-        <v>-4.8780487804878003</v>
+        <v>-2.5641025641025599</v>
       </c>
       <c r="D39" s="5">
-        <v>-2.228048782598497E-2</v>
+        <v>-1.1140243923076904E-2</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1882,545 +1881,545 @@
         <v>62</v>
       </c>
       <c r="B40" s="19">
-        <v>0.43804314255422716</v>
+        <v>0.41539203800000002</v>
       </c>
       <c r="C40" s="15">
-        <v>-5.1709758131776402</v>
+        <v>0</v>
       </c>
       <c r="D40" s="5">
-        <v>-2.2651104952762336E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B41">
-        <v>0.43099999990430621</v>
+      <c r="B41" s="19">
+        <v>0.43169741099999998</v>
       </c>
       <c r="C41" s="15">
-        <v>0.16181229773462699</v>
+        <v>-2.1001615508885298</v>
       </c>
       <c r="D41" s="5">
-        <v>6.9741100308139809E-4</v>
+        <v>-9.06634304200323E-3</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B42">
-        <v>0.39915608860803065</v>
+      <c r="B42" s="19">
+        <v>0.43892069299999997</v>
       </c>
       <c r="C42" s="15">
-        <v>9.9621689785624206</v>
+        <v>-9.9770642201834807</v>
       </c>
       <c r="D42" s="5">
-        <v>3.9764604035352355E-2</v>
+        <v>-4.3791399416284377E-2</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B43">
-        <v>0.37545160620814483</v>
+      <c r="B43" s="19">
+        <v>0.38129521100000002</v>
       </c>
       <c r="C43" s="15">
-        <v>1.5564202334630299</v>
+        <v>-4.2145593869731801</v>
       </c>
       <c r="D43" s="5">
-        <v>5.843604765885504E-3</v>
+        <v>-1.6069913107279694E-2</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="B44">
-        <v>0.35488409544593391</v>
+      <c r="B44" s="19">
+        <v>0.34629819000000001</v>
       </c>
       <c r="C44" s="15">
-        <v>-2.4193548387096699</v>
+        <v>-3.7649219467401198</v>
       </c>
       <c r="D44" s="5">
-        <v>-8.5859055349822456E-3</v>
+        <v>-1.30378565564738E-2</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="B45">
-        <v>0.34381194679865207</v>
+      <c r="B45" s="19">
+        <v>0.34007485999999998</v>
       </c>
       <c r="C45" s="15">
-        <v>-1.0869565217391299</v>
+        <v>-3.2967032967032899</v>
       </c>
       <c r="D45" s="5">
-        <v>-3.7370863782462166E-3</v>
+        <v>-1.1211259120879098E-2</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="B46">
-        <v>0.33318370060261193</v>
+      <c r="B46" s="19">
+        <v>0.32527058800000003</v>
       </c>
       <c r="C46" s="15">
-        <v>-2.375</v>
+        <v>-4.6734955185659404</v>
       </c>
       <c r="D46" s="5">
-        <v>-7.9131128893120337E-3</v>
+        <v>-1.5201506353393084E-2</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="B47">
-        <v>0.3297556176203652</v>
+      <c r="B47" s="19">
+        <v>0.322708785</v>
       </c>
       <c r="C47" s="15">
-        <v>-2.13698630136986</v>
+        <v>-3.9193729003359401</v>
       </c>
       <c r="D47" s="5">
-        <v>-7.0468323765447809E-3</v>
+        <v>-1.2648160666293373E-2</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B48">
-        <v>0.23502103551536174</v>
+      <c r="B48" s="19">
+        <v>0.21160512500000001</v>
       </c>
       <c r="C48" s="15">
-        <v>-9.9633251833740797</v>
+        <v>-9.9796334012219905</v>
       </c>
       <c r="D48" s="5">
-        <v>-2.3415910017728577E-2</v>
+        <v>-2.1117415733197545E-2</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="B49">
-        <v>0.32905624227702701</v>
+      <c r="B49" s="19">
+        <v>0.30883587400000001</v>
       </c>
       <c r="C49" s="15">
-        <v>-6.1449579831932697</v>
+        <v>-5.2042529378847204</v>
       </c>
       <c r="D49" s="5">
-        <v>-2.022036782899796E-2</v>
+        <v>-1.6072600045886953E-2</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="B50">
-        <v>0.3513732545227799</v>
+      <c r="B50" s="19">
+        <v>0.33685134500000002</v>
       </c>
       <c r="C50" s="15">
-        <v>-4.1329011345218802</v>
+        <v>-4.1420118343195202</v>
       </c>
       <c r="D50" s="5">
-        <v>-1.4521909222578424E-2</v>
+        <v>-1.3952422573964476E-2</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="B51">
-        <v>0.29509426884476536</v>
+      <c r="B51" s="19">
+        <v>0.27836336900000003</v>
       </c>
       <c r="C51" s="15">
-        <v>-5.6696795398520896</v>
+        <v>-4.4425087108013903</v>
       </c>
       <c r="D51" s="5">
-        <v>-1.6730899383967782E-2</v>
+        <v>-1.2366316915505217E-2</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B52">
-        <v>0.25703939381613511</v>
+      <c r="B52" s="19">
+        <v>0.25281408900000002</v>
       </c>
       <c r="C52" s="15">
-        <v>-1.6438356164383501</v>
+        <v>-4.7353760445682402</v>
       </c>
       <c r="D52" s="5">
-        <v>-4.2253051038268633E-3</v>
+        <v>-1.1971697807799431E-2</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B53">
-        <v>0.23751240359060399</v>
+      <c r="B53" s="19">
+        <v>0.23632314300000001</v>
       </c>
       <c r="C53" s="15">
-        <v>-0.50071530758226002</v>
+        <v>-8.8425593098490296</v>
       </c>
       <c r="D53" s="5">
-        <v>-1.1892609621847116E-3</v>
+        <v>-2.0897014082674335E-2</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B54">
-        <v>0.18735091994996875</v>
+      <c r="B54" s="19">
+        <v>0.184144425</v>
       </c>
       <c r="C54" s="15">
-        <v>-1.7114914425427801</v>
+        <v>-6.9651741293532297</v>
       </c>
       <c r="D54" s="5">
-        <v>-3.2064949624688891E-3</v>
+        <v>-1.2825979850746261E-2</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B55">
-        <v>0.20288589635251797</v>
+      <c r="B55" s="19">
+        <v>0.20247477999999999</v>
       </c>
       <c r="C55" s="15">
-        <v>-0.202634245187436</v>
+        <v>-3.6548223350253801</v>
       </c>
       <c r="D55" s="5">
-        <v>-4.1111630466568856E-4</v>
+        <v>-7.4000934822335005E-3</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B56">
-        <v>0.16093179927742837</v>
+      <c r="B56" s="19">
+        <v>0.156684669</v>
       </c>
       <c r="C56" s="15">
-        <v>-2.63908701854493</v>
+        <v>-5.1282051282051198</v>
       </c>
       <c r="D56" s="5">
-        <v>-4.2471302234413956E-3</v>
+        <v>-8.0351112307692173E-3</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B57">
-        <v>0.17204900415384616</v>
+      <c r="B57" s="19">
+        <v>0.17937023799999999</v>
       </c>
       <c r="C57" s="15">
-        <v>4.2553191489361701</v>
+        <v>-4.7619047619047601</v>
       </c>
       <c r="D57" s="5">
-        <v>7.3212342193126022E-3</v>
+        <v>-8.5414399047619004E-3</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B58">
-        <v>0.15980392150537631</v>
+      <c r="B58" s="19">
+        <v>0.15787469900000001</v>
       </c>
       <c r="C58" s="15">
-        <v>-1.2072434607645799</v>
+        <v>-1.73116089613034</v>
       </c>
       <c r="D58" s="5">
-        <v>-1.9292223924190178E-3</v>
+        <v>-2.7330650539714768E-3</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B59">
-        <v>0.14105187790393012</v>
+      <c r="B59" s="19">
+        <v>0.12855961499999999</v>
       </c>
       <c r="C59" s="15">
-        <v>-8.8565022421524606</v>
+        <v>-5.9655596555965502</v>
       </c>
       <c r="D59" s="5">
-        <v>-1.2492262729159723E-2</v>
+        <v>-7.6693005258302504E-3</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B60">
-        <v>0.13142613563858696</v>
+      <c r="B60" s="19">
+        <v>0.12855343299999999</v>
       </c>
       <c r="C60" s="15">
-        <v>-2.1857923497267699</v>
+        <v>-5.1210428305400297</v>
       </c>
       <c r="D60" s="5">
-        <v>-2.8727024183297619E-3</v>
+        <v>-6.5832763640595801E-3</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B61">
-        <v>0.12738620681256893</v>
+      <c r="B61" s="19">
+        <v>0.121049672</v>
       </c>
       <c r="C61" s="15">
-        <v>-4.9742710120068603</v>
+        <v>0</v>
       </c>
       <c r="D61" s="5">
-        <v>-6.3365351587727249E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B62">
-        <v>0.11492420168865648</v>
+      <c r="B62" s="19">
+        <v>0.10348757</v>
       </c>
       <c r="C62" s="15">
-        <v>-9.9514563106796103</v>
+        <v>0.62893081761006298</v>
       </c>
       <c r="D62" s="5">
-        <v>-1.1436631721443968E-2</v>
+        <v>6.5086522012578623E-4</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B63">
-        <v>9.3725000271893247E-2</v>
+      <c r="B63" s="19">
+        <v>9.0058886000000005E-2</v>
       </c>
       <c r="C63" s="15">
-        <v>-3.9115646258503398</v>
+        <v>-3.6283185840707901</v>
       </c>
       <c r="D63" s="5">
-        <v>-3.6661139562135111E-3</v>
+        <v>-3.2676232973451276E-3</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B64">
-        <v>9.6279841516905079E-2</v>
+      <c r="B64" s="19">
+        <v>9.4563963000000001E-2</v>
       </c>
       <c r="C64" s="15">
-        <v>-1.78217821782178</v>
+        <v>-3.0913978494623602</v>
       </c>
       <c r="D64" s="5">
-        <v>-1.7158783636676131E-3</v>
+        <v>-2.9233483185483822E-3</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B65">
-        <v>9.1278604930630197E-2</v>
+      <c r="B65" s="19">
+        <v>9.2286329E-2</v>
       </c>
       <c r="C65" s="15">
-        <v>1.1040092969203901</v>
+        <v>-10</v>
       </c>
       <c r="D65" s="5">
-        <v>1.007724284533391E-3</v>
+        <v>-9.2286329000000004E-3</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B66">
-        <v>6.1738829475E-2</v>
+      <c r="B66" s="19">
+        <v>6.2085243999999998E-2</v>
       </c>
       <c r="C66" s="15">
-        <v>0.56109725685785505</v>
+        <v>-3.28580285182889</v>
       </c>
       <c r="D66" s="5">
-        <v>3.4641487860037385E-4</v>
+        <v>-2.0399987179169246E-3</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B67">
-        <v>5.7750000076693231E-2</v>
+      <c r="B67" s="19">
+        <v>5.4377399999999999E-2</v>
       </c>
       <c r="C67" s="15">
-        <v>-5.84</v>
+        <v>-2.1240441801189398</v>
       </c>
       <c r="D67" s="5">
-        <v>-3.3726000044788846E-3</v>
+        <v>-1.1549999999999963E-3</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B68">
-        <v>5.9018448440462425E-2</v>
+      <c r="B68" s="19">
+        <v>5.6951135999999999E-2</v>
       </c>
       <c r="C68" s="15">
-        <v>-3.5028248587570601</v>
+        <v>-3.8641686182669699</v>
       </c>
       <c r="D68" s="5">
-        <v>-2.0673128832252364E-3</v>
+        <v>-2.200687925058543E-3</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B69">
-        <v>4.9262573662162162E-2</v>
+      <c r="B69" s="19">
+        <v>4.8370750999999997E-2</v>
       </c>
       <c r="C69" s="15">
-        <v>-1.8103448275862</v>
+        <v>4.1264266900790103</v>
       </c>
       <c r="D69" s="5">
-        <v>-8.9182245422879435E-4</v>
+        <v>1.9959835794556595E-3</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B70">
-        <v>4.9357009255996516E-2</v>
+      <c r="B70" s="19">
+        <v>4.8470615000000002E-2</v>
       </c>
       <c r="C70" s="15">
-        <v>-1.79588261060008</v>
+        <v>-4.0588760035682396</v>
       </c>
       <c r="D70" s="5">
-        <v>-8.8639394634071333E-4</v>
+        <v>-1.9673621610169479E-3</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B71">
-        <v>4.6701881560563381E-2</v>
+      <c r="B71" s="19">
+        <v>4.5534335000000002E-2</v>
       </c>
       <c r="C71" s="15">
-        <v>-2.5</v>
+        <v>-3.22344322344322</v>
       </c>
       <c r="D71" s="5">
-        <v>-1.1675470390140844E-3</v>
+        <v>-1.4677734358974346E-3</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B72">
-        <v>4.079287255538222E-2</v>
+      <c r="B72" s="19">
+        <v>4.0338416000000002E-2</v>
       </c>
       <c r="C72" s="15">
-        <v>-1.11405835543766</v>
+        <v>-4.3454935622317503</v>
       </c>
       <c r="D72" s="5">
-        <v>-4.5445640512627172E-4</v>
+        <v>-1.7529032703862623E-3</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B73">
-        <v>3.9484033971924022E-2</v>
+      <c r="B73" s="19">
+        <v>3.6503475000000001E-2</v>
       </c>
       <c r="C73" s="15">
-        <v>-7.5487701441899899</v>
+        <v>2.5688073394495401</v>
       </c>
       <c r="D73" s="5">
-        <v>-2.9805589681944338E-3</v>
+        <v>9.3770394495412798E-4</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B74">
-        <v>2.5465116479057588E-2</v>
+      <c r="B74" s="19">
+        <v>2.4942332000000001E-2</v>
       </c>
       <c r="C74" s="15">
-        <v>-2.0529443544030199</v>
+        <v>1.7650303364589</v>
       </c>
       <c r="D74" s="5">
-        <v>-5.2278467109896588E-4</v>
+        <v>4.4023972642029592E-4</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B75">
-        <v>2.5703760328500001E-2</v>
+      <c r="B75" s="19">
+        <v>2.3940174000000002E-2</v>
       </c>
       <c r="C75" s="15">
-        <v>-6.8611987381703399</v>
+        <v>-5.3344623200677397</v>
       </c>
       <c r="D75" s="5">
-        <v>-1.7635860793213704E-3</v>
+        <v>-1.2770795613886539E-3</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B76">
-        <v>1.9066016770287676E-2</v>
+      <c r="B76" s="19">
+        <v>1.8830533999999999E-2</v>
       </c>
       <c r="C76" s="15">
-        <v>-1.2350936967632</v>
+        <v>-2.9754204398447599</v>
       </c>
       <c r="D76" s="5">
-        <v>-2.3548317135363772E-4</v>
+        <v>-5.602875575679171E-4</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B77">
-        <v>2.0390493393841167E-2</v>
+      <c r="B77" s="19">
+        <v>1.9798237999999999E-2</v>
       </c>
       <c r="C77" s="15">
-        <v>-2.9045643153526899</v>
+        <v>-5.1282051282051198</v>
       </c>
       <c r="D77" s="5">
-        <v>-5.9225499484185816E-4</v>
+        <v>-1.0152942564102547E-3</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B78">
-        <v>1.9698731879161111</v>
+      <c r="B78" s="19">
+        <v>2.0020301489999999</v>
       </c>
       <c r="C78" s="15">
-        <v>1.63243812532912</v>
+        <v>0.62176165803108796</v>
       </c>
       <c r="D78" s="5">
-        <v>3.2156960940178739E-2</v>
+        <v>1.2447855848704661E-2</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -2428,11 +2427,11 @@
         <v>23</v>
       </c>
       <c r="B79" s="7">
-        <v>105.45617682171583</v>
+        <v>105.53302846300001</v>
       </c>
       <c r="C79" s="6"/>
       <c r="D79" s="7">
-        <v>7.6851649580997175E-2</v>
+        <v>-0.28999999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -2470,10 +2469,10 @@
         <v>5.6067999999999998</v>
       </c>
       <c r="C2" s="8">
-        <v>-9.9606077658975796</v>
+        <v>-10</v>
       </c>
       <c r="D2" s="5">
-        <v>-0.55847135621834543</v>
+        <v>-0.56067999999999996</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2484,10 +2483,10 @@
         <v>12.783636363636365</v>
       </c>
       <c r="C3" s="8">
-        <v>6.09756097560975</v>
+        <v>3.44827586206896</v>
       </c>
       <c r="D3" s="5">
-        <v>0.77949002217294838</v>
+        <v>0.44081504702194296</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2498,10 +2497,10 @@
         <v>11.325483692647872</v>
       </c>
       <c r="C4" s="8">
-        <v>3.87096774193548</v>
+        <v>3.1055900621118</v>
       </c>
       <c r="D4" s="5">
-        <v>0.4384058203605623</v>
+        <v>0.35172309604496482</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2512,10 +2511,10 @@
         <v>11.056410256410254</v>
       </c>
       <c r="C5" s="8">
-        <v>-10</v>
+        <v>-9.9537037037037006</v>
       </c>
       <c r="D5" s="5">
-        <v>-1.1056410256410254</v>
+        <v>-1.1005223171889833</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2526,10 +2525,10 @@
         <v>6.10093572009764</v>
       </c>
       <c r="C6" s="8">
-        <v>4.0972222222222197</v>
+        <v>4.6697798532354904</v>
       </c>
       <c r="D6" s="5">
-        <v>0.24996889408733369</v>
+        <v>0.28490026711596722</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2540,10 +2539,10 @@
         <v>6.185991902834008</v>
       </c>
       <c r="C7" s="8">
-        <v>3.16831683168316</v>
+        <v>4.4145873320537401</v>
       </c>
       <c r="D7" s="5">
-        <v>0.19599182266404724</v>
+        <v>0.27308601490438023</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2554,10 +2553,10 @@
         <v>5.4177435897435906</v>
       </c>
       <c r="C8" s="8">
-        <v>3.8277511961722399</v>
+        <v>7.3732718894009199</v>
       </c>
       <c r="D8" s="5">
-        <v>0.20737774506195514</v>
+        <v>0.3994649651423845</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2568,10 +2567,10 @@
         <v>2.8229684210526313</v>
       </c>
       <c r="C9" s="8">
-        <v>1.4925373134328299</v>
+        <v>1.9607843137254899</v>
       </c>
       <c r="D9" s="5">
-        <v>4.2133857030636122E-2</v>
+        <v>5.5352321981424132E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2582,10 +2581,10 @@
         <v>2.6673319148936168</v>
       </c>
       <c r="C10" s="8">
-        <v>0.66666666666666596</v>
+        <v>-1.0347682119205199</v>
       </c>
       <c r="D10" s="5">
-        <v>1.7782212765957425E-2</v>
+        <v>-2.7600702761730041E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2596,10 +2595,10 @@
         <v>1.3113394683026585</v>
       </c>
       <c r="C11" s="8">
-        <v>4.9610894941634198</v>
+        <v>3.7998146431881299</v>
       </c>
       <c r="D11" s="5">
-        <v>6.5056724594781637E-2</v>
+        <v>4.9828469138469778E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2610,10 +2609,10 @@
         <v>1.1868852459016395</v>
       </c>
       <c r="C12" s="8">
-        <v>-0.163487738419618</v>
+        <v>-5.3493449781659299</v>
       </c>
       <c r="D12" s="5">
-        <v>-1.9404118461607122E-3</v>
+        <v>-6.3490586298231705E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2624,10 +2623,10 @@
         <v>1.231483870967742</v>
       </c>
       <c r="C13" s="8">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="D13" s="5">
-        <v>-3.0787096774193553E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2638,10 +2637,10 @@
         <v>0.28472795497185743</v>
       </c>
       <c r="C14" s="8">
-        <v>-1.6438356164383501</v>
+        <v>-4.7353760445682402</v>
       </c>
       <c r="D14" s="5">
-        <v>-4.6804595337839403E-3</v>
+        <v>-1.3482939371926383E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2652,10 +2651,10 @@
         <v>0.20598086124401913</v>
       </c>
       <c r="C15" s="8">
-        <v>0.16181229773462699</v>
+        <v>-2.1001615508885298</v>
       </c>
       <c r="D15" s="5">
-        <v>3.3330236447252112E-4</v>
+        <v>-4.3259308500359431E-3</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2666,10 +2665,10 @@
         <v>0.18893656716417911</v>
       </c>
       <c r="C16" s="8">
-        <v>-2.375</v>
+        <v>-4.6734955185659404</v>
       </c>
       <c r="D16" s="5">
-        <v>-4.4872434701492539E-3</v>
+        <v>-8.8299419993502389E-3</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2680,10 +2679,10 @@
         <v>0.18752732951587717</v>
       </c>
       <c r="C17" s="8">
-        <v>-0.36726128016789</v>
+        <v>-4.8973143759873601</v>
       </c>
       <c r="D17" s="5">
-        <v>-6.8871527104466795E-4</v>
+        <v>-9.1838028672862407E-3</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2694,10 +2693,10 @@
         <v>0.16901162790697674</v>
       </c>
       <c r="C18" s="8">
-        <v>-1.5820149875103999</v>
+        <v>-3.4686971235194499</v>
       </c>
       <c r="D18" s="5">
-        <v>-2.6737892841236814E-3</v>
+        <v>-5.8625014756226975E-3</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2708,10 +2707,10 @@
         <v>0.15850839030453698</v>
       </c>
       <c r="C19" s="8">
-        <v>-5.3968253968253901</v>
+        <v>1.20805369127516</v>
       </c>
       <c r="D19" s="5">
-        <v>-8.5544210640543655E-3</v>
+        <v>1.9148664600547969E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2722,10 +2721,10 @@
         <v>0.13078455039227521</v>
       </c>
       <c r="C20" s="8">
-        <v>0.544135429262394</v>
+        <v>-0.78171978352375204</v>
       </c>
       <c r="D20" s="5">
-        <v>7.1164507468589875E-4</v>
+        <v>-1.0223687042090061E-3</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2736,10 +2735,10 @@
         <v>0.12966734902763563</v>
       </c>
       <c r="C21" s="8">
-        <v>-1.3705583756345101</v>
+        <v>-1.54400411734431</v>
       </c>
       <c r="D21" s="5">
-        <v>-1.7771667125614937E-3</v>
+        <v>-2.0020692078379114E-3</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2750,10 +2749,10 @@
         <v>0.12070175438596491</v>
       </c>
       <c r="C22" s="8">
-        <v>-1.15008625646923</v>
+        <v>-3.2577079697498501</v>
       </c>
       <c r="D22" s="5">
-        <v>-1.3881742885102286E-3</v>
+        <v>-3.9321106722594677E-3</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2764,10 +2763,10 @@
         <v>0.10357262103505845</v>
       </c>
       <c r="C23" s="8">
-        <v>2.08092485549132</v>
+        <v>-9.9660249150622793</v>
       </c>
       <c r="D23" s="5">
-        <v>2.1552684146023625E-3</v>
+        <v>-1.032207321753696E-2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2778,10 +2777,10 @@
         <v>6.9184372858122012E-2</v>
       </c>
       <c r="C24" s="8">
-        <v>-0.20632737276478599</v>
+        <v>-4.1350792556857296</v>
       </c>
       <c r="D24" s="5">
-        <v>-1.4274629888195683E-4</v>
+        <v>-2.8608286502324713E-3</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2792,10 +2791,10 @@
         <v>4.9667957941339241E-2</v>
       </c>
       <c r="C25" s="8">
-        <v>-2.13698630136986</v>
+        <v>-3.9193729003359401</v>
       </c>
       <c r="D25" s="5">
-        <v>-1.0613974573765632E-3</v>
+        <v>-1.9466724837031027E-3</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2806,10 +2805,10 @@
         <v>3.8065054211843204E-2</v>
       </c>
       <c r="C26" s="8">
-        <v>-3.9115646258503398</v>
+        <v>-3.6283185840707901</v>
       </c>
       <c r="D26" s="5">
-        <v>-1.4889391953612136E-3</v>
+        <v>-1.3811214360049278E-3</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2820,10 +2819,10 @@
         <v>4.0107286544479211E-2</v>
       </c>
       <c r="C27" s="8">
-        <v>0</v>
+        <v>-2.97117516629711</v>
       </c>
       <c r="D27" s="5">
-        <v>0</v>
+        <v>-1.1916577376851886E-3</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2834,10 +2833,10 @@
         <v>3.9482758620689659E-2</v>
       </c>
       <c r="C28" s="8">
-        <v>-0.64608758076094697</v>
+        <v>-3.4682080924855399</v>
       </c>
       <c r="D28" s="5">
-        <v>-2.5509319999009807E-4</v>
+        <v>-1.369344229619291E-3</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2848,10 +2847,10 @@
         <v>2.9939999999999998E-2</v>
       </c>
       <c r="C29" s="8">
-        <v>-1.25361620057859</v>
+        <v>-2.9296875</v>
       </c>
       <c r="D29" s="5">
-        <v>-3.7533269045322983E-4</v>
+        <v>-8.7714843749999989E-4</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -2862,10 +2861,10 @@
         <v>2.9798957557706625E-2</v>
       </c>
       <c r="C30" s="8">
-        <v>-0.22354694485842</v>
+        <v>-4.5556385362210596</v>
       </c>
       <c r="D30" s="5">
-        <v>-6.6614659219910413E-5</v>
+        <v>-1.3575327938910409E-3</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2876,10 +2875,10 @@
         <v>2.775800711743772E-2</v>
       </c>
       <c r="C31" s="8">
-        <v>-1.6252390057361299</v>
+        <v>-3.79008746355685</v>
       </c>
       <c r="D31" s="5">
-        <v>-4.5113395888760901E-4</v>
+        <v>-1.0520527478912252E-3</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2890,10 +2889,10 @@
         <v>2.0293040293040292E-2</v>
       </c>
       <c r="C32" s="8">
-        <v>4.2553191489361701</v>
+        <v>-4.7619047619047601</v>
       </c>
       <c r="D32" s="5">
-        <v>8.6353362949107633E-4</v>
+        <v>-9.663352520495373E-4</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -2904,10 +2903,10 @@
         <v>1.9945652173913045E-2</v>
       </c>
       <c r="C33" s="8">
-        <v>-2.1857923497267699</v>
+        <v>-5.1210428305400297</v>
       </c>
       <c r="D33" s="5">
-        <v>-4.3597053932050252E-4</v>
+        <v>-1.0214253906566256E-3</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -2918,10 +2917,10 @@
         <v>1.9643334819438255E-2</v>
       </c>
       <c r="C34" s="8">
-        <v>-3.24588706091596</v>
+        <v>-2.5735294117646998</v>
       </c>
       <c r="D34" s="5">
-        <v>-6.376004632365458E-4</v>
+        <v>-5.0552699902965985E-4</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2932,10 +2931,10 @@
         <v>1.9981949458483753E-2</v>
       </c>
       <c r="C35" s="8">
-        <v>-5.6696795398520896</v>
+        <v>-4.4425087108013903</v>
       </c>
       <c r="D35" s="5">
-        <v>-1.1329125001112387E-3</v>
+        <v>-8.8769984528107196E-4</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2946,10 +2945,10 @@
         <v>1.9511614055985706E-2</v>
       </c>
       <c r="C36" s="8">
-        <v>-1.3277006638503299</v>
+        <v>-4.0978593272171198</v>
       </c>
       <c r="D36" s="5">
-        <v>-2.5905582934923648E-4</v>
+        <v>-7.9955849648381675E-4</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2960,10 +2959,10 @@
         <v>1.9461966604823747E-2</v>
       </c>
       <c r="C37" s="8">
-        <v>-2.6095060577819198</v>
+        <v>-3.4449760765550201</v>
       </c>
       <c r="D37" s="5">
-        <v>-5.0786119751636998E-4</v>
+        <v>-6.7046009356330543E-4</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2974,10 +2973,10 @@
         <v>1.9587194608256111E-2</v>
       </c>
       <c r="C38" s="8">
-        <v>-1.0869565217391299</v>
+        <v>-3.2967032967032899</v>
       </c>
       <c r="D38" s="5">
-        <v>-2.12904289220175E-4</v>
+        <v>-6.4573169038206822E-4</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2988,10 +2987,10 @@
         <v>2.0102367242482405E-2</v>
       </c>
       <c r="C39" s="8">
-        <v>1.4677728142948301</v>
+        <v>-2.2012578616352201</v>
       </c>
       <c r="D39" s="5">
-        <v>2.95057081414866E-4</v>
+        <v>-4.4250493929992715E-4</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -3003,7 +3002,7 @@
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="7">
-        <v>0.27244848292001128</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -3056,10 +3055,10 @@
         <v>8.142475703550101</v>
       </c>
       <c r="C2" s="4">
-        <v>4.9610894941634198</v>
+        <v>3.7998146431881299</v>
       </c>
       <c r="D2" s="5">
-        <v>0.40395550669363312</v>
+        <v>0.30939898410153244</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -3070,10 +3069,10 @@
         <v>6.3482250682462382</v>
       </c>
       <c r="C3" s="4">
-        <v>-9.9606077658975796</v>
+        <v>-10</v>
       </c>
       <c r="D3" s="5">
-        <v>-0.63232179914439168</v>
+        <v>-0.63482250682462382</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -3084,10 +3083,10 @@
         <v>7.1320325203886634</v>
       </c>
       <c r="C4" s="4">
-        <v>3.16831683168316</v>
+        <v>4.4145873320537401</v>
       </c>
       <c r="D4" s="5">
-        <v>0.22596538678459072</v>
+        <v>0.31484980416303104</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -3098,10 +3097,10 @@
         <v>4.5357012361152904</v>
       </c>
       <c r="C5" s="4">
-        <v>1.1040092969203901</v>
+        <v>-10</v>
       </c>
       <c r="D5" s="5">
-        <v>5.0074563327245858E-2</v>
+        <v>-0.45357012361152904</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -3112,10 +3111,10 @@
         <v>9.0120080054025973</v>
       </c>
       <c r="C6" s="4">
-        <v>6.09756097560975</v>
+        <v>3.44827586206896</v>
       </c>
       <c r="D6" s="5">
-        <v>0.54951268325625546</v>
+        <v>0.3107588967380201</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -3126,10 +3125,10 @@
         <v>2.4815613914160055</v>
       </c>
       <c r="C7" s="4">
-        <v>-1.9073569482288799</v>
+        <v>-2.9166666666666599</v>
       </c>
       <c r="D7" s="5">
-        <v>-4.7332233623738451E-2</v>
+        <v>-7.2378873916299991E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -3140,10 +3139,10 @@
         <v>2.3103420198519116</v>
       </c>
       <c r="C8" s="4">
-        <v>4.0972222222222197</v>
+        <v>4.6697798532354904</v>
       </c>
       <c r="D8" s="5">
-        <v>9.4659846646710205E-2</v>
+        <v>0.10788788618387846</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -3154,10 +3153,10 @@
         <v>4.2133333333333329</v>
       </c>
       <c r="C9" s="4">
-        <v>-10</v>
+        <v>-9.9537037037037006</v>
       </c>
       <c r="D9" s="5">
-        <v>-0.42133333333333328</v>
+        <v>-0.4193827160493826</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -3168,10 +3167,10 @@
         <v>1.1190319312359234</v>
       </c>
       <c r="C10" s="4">
-        <v>0.29239766081871299</v>
+        <v>-2.5072886297375998</v>
       </c>
       <c r="D10" s="5">
-        <v>3.2720231907483088E-3</v>
+        <v>-2.8057360375011383E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -3182,10 +3181,10 @@
         <v>9.1340705128547377</v>
       </c>
       <c r="C11" s="4">
-        <v>1.4925373134328299</v>
+        <v>1.9607843137254899</v>
       </c>
       <c r="D11" s="5">
-        <v>0.13632941063962239</v>
+        <v>0.17909942182068112</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -3196,10 +3195,10 @@
         <v>10.049098711951913</v>
       </c>
       <c r="C12" s="4">
-        <v>0.66666666666666596</v>
+        <v>-1.0347682119205199</v>
       </c>
       <c r="D12" s="5">
-        <v>6.6993991413012682E-2</v>
+        <v>-0.10398487905579282</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -3210,10 +3209,10 @@
         <v>1.9973847169987202</v>
       </c>
       <c r="C13" s="4">
-        <v>1.4677728142948301</v>
+        <v>-2.2012578616352201</v>
       </c>
       <c r="D13" s="5">
-        <v>2.9317069872986944E-2</v>
+        <v>-4.3967588110034719E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -3224,10 +3223,10 @@
         <v>2.391</v>
       </c>
       <c r="C14" s="4">
-        <v>-5.3968253968253901</v>
+        <v>1.20805369127516</v>
       </c>
       <c r="D14" s="5">
-        <v>-0.12903809523809509</v>
+        <v>2.8884563758389076E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -3238,10 +3237,10 @@
         <v>1.2620487802271294</v>
       </c>
       <c r="C15" s="4">
-        <v>-0.488599348534202</v>
+        <v>-2.9459901800327302</v>
       </c>
       <c r="D15" s="5">
-        <v>-6.1663621183735973E-3</v>
+        <v>-3.7179833132714085E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -3252,10 +3251,10 @@
         <v>1.8909569077519615</v>
       </c>
       <c r="C16" s="4">
-        <v>0.544135429262394</v>
+        <v>-0.78171978352375204</v>
       </c>
       <c r="D16" s="5">
-        <v>1.0289366487163028E-2</v>
+        <v>-1.4781984245806068E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -3266,10 +3265,10 @@
         <v>1.2658122062682029</v>
       </c>
       <c r="C17" s="4">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="D17" s="5">
-        <v>-3.1645305156705071E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -3280,10 +3279,10 @@
         <v>1.606964380508197</v>
       </c>
       <c r="C18" s="11">
-        <v>-0.163487738419618</v>
+        <v>-5.3493449781659299</v>
       </c>
       <c r="D18" s="5">
-        <v>-2.6271897229016763E-3</v>
+        <v>-8.5962068389630483E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -3294,10 +3293,10 @@
         <v>1.2853032785581395</v>
       </c>
       <c r="C19" s="11">
-        <v>-1.5820149875103999</v>
+        <v>-3.4686971235194499</v>
       </c>
       <c r="D19" s="5">
-        <v>-2.0333690501752311E-2</v>
+        <v>-4.4583277851847368E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -3308,10 +3307,10 @@
         <v>1.0374311923900574</v>
       </c>
       <c r="C20" s="11">
-        <v>9.9621689785624206</v>
+        <v>-9.9770642201834807</v>
       </c>
       <c r="D20" s="5">
-        <v>0.10335064842221252</v>
+        <v>-0.10350517630497126</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -3322,10 +3321,10 @@
         <v>1.1690539052194047</v>
       </c>
       <c r="C21" s="11">
-        <v>-4.9742710120068603</v>
+        <v>0</v>
       </c>
       <c r="D21" s="5">
-        <v>-5.8151909522062999E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -3336,10 +3335,10 @@
         <v>0.35488986740425527</v>
       </c>
       <c r="C22" s="11">
-        <v>-2.9264214046822699</v>
+        <v>-0.68906115417743297</v>
       </c>
       <c r="D22" s="5">
-        <v>-1.0385573042766652E-2</v>
+        <v>-2.445408216394523E-3</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -3350,10 +3349,10 @@
         <v>0.26922888663105177</v>
       </c>
       <c r="C23" s="11">
-        <v>2.08092485549132</v>
+        <v>-9.9660249150622793</v>
       </c>
       <c r="D23" s="5">
-        <v>5.602450820068103E-3</v>
+        <v>-2.6831417920195399E-2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -3364,10 +3363,10 @@
         <v>8.7351351015384632E-2</v>
       </c>
       <c r="C24" s="11">
-        <v>3.8277511961722399</v>
+        <v>7.3732718894009199</v>
       </c>
       <c r="D24" s="5">
-        <v>3.3435923833639975E-3</v>
+        <v>6.4406526094292803E-3</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -3378,10 +3377,10 @@
         <v>0.819736841846324</v>
       </c>
       <c r="C25" s="11">
-        <v>3.87096774193548</v>
+        <v>3.1055900621118</v>
       </c>
       <c r="D25" s="5">
-        <v>3.1731748716631862E-2</v>
+        <v>2.5457665895848559E-2</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -3392,10 +3391,10 @@
         <v>0.63076923069377988</v>
       </c>
       <c r="C26" s="11">
-        <v>0.16181229773462699</v>
+        <v>-2.1001615508885298</v>
       </c>
       <c r="D26" s="5">
-        <v>1.0206621855886353E-3</v>
+        <v>-1.3247172857866136E-2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -3406,10 +3405,10 @@
         <v>0.40829875493806767</v>
       </c>
       <c r="C27" s="11">
-        <v>-7.5487701441899899</v>
+        <v>2.5688073394495401</v>
       </c>
       <c r="D27" s="5">
-        <v>-3.0821534511864302E-2</v>
+        <v>1.0488408383730174E-2</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -3420,10 +3419,10 @@
         <v>6.1546391343598066E-2</v>
       </c>
       <c r="C28" s="11">
-        <v>-2.9045643153526899</v>
+        <v>-5.1282051282051198</v>
       </c>
       <c r="D28" s="5">
-        <v>-1.7876545203534663E-3</v>
+        <v>-3.1562251971075875E-3</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -3434,10 +3433,10 @@
         <v>5.8339222449871463E-2</v>
       </c>
       <c r="C29" s="11">
-        <v>-3.56662180349932</v>
+        <v>-9.2812281926029296</v>
       </c>
       <c r="D29" s="5">
-        <v>-2.0807394278890856E-3</v>
+        <v>-5.4145963613628076E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -3448,10 +3447,10 @@
         <v>5.8486238340517235E-2</v>
       </c>
       <c r="C30" s="11">
-        <v>1.0948905109489</v>
+        <v>9.7472924187725596</v>
       </c>
       <c r="D30" s="5">
-        <v>6.4036027380128067E-4</v>
+        <v>5.7008246757904871E-3</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -3462,10 +3461,10 @@
         <v>2.0676403161819536E-2</v>
       </c>
       <c r="C31" s="11">
-        <v>-0.50071530758226002</v>
+        <v>-8.8425593098490296</v>
       </c>
       <c r="D31" s="5">
-        <v>-1.0352991568865282E-4</v>
+        <v>-1.8283232127273923E-3</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -3476,10 +3475,10 @@
         <v>2.6674678674000001</v>
       </c>
       <c r="C32" s="11">
-        <v>0.24</v>
+        <v>0.34</v>
       </c>
       <c r="D32" s="5">
-        <v>6.4019228817600001E-3</v>
+        <v>9.0693907491600015E-3</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -3490,10 +3489,10 @@
         <v>2.4571638431999996</v>
       </c>
       <c r="C33" s="11">
-        <v>0.78</v>
+        <v>0.71</v>
       </c>
       <c r="D33" s="5">
-        <v>1.9165877976959997E-2</v>
+        <v>1.7445863286719997E-2</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -3504,10 +3503,10 @@
         <v>2.3318555208</v>
       </c>
       <c r="C34" s="11">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="D34" s="5">
-        <v>3.8009244989039993E-2</v>
+        <v>3.9408358301520001E-2</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -3519,7 +3518,7 @@
       </c>
       <c r="C35" s="6"/>
       <c r="D35" s="7">
-        <v>0.38550740718147886</v>
+        <v>-0.53</v>
       </c>
     </row>
   </sheetData>
@@ -3551,13 +3550,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="19">
-        <v>56.092996816771858</v>
+        <v>56.710761099999999</v>
       </c>
       <c r="C2" s="8">
-        <v>1.10132158590308</v>
+        <v>0.21786492374727601</v>
       </c>
       <c r="D2" s="9">
-        <v>0.61776428212303602</v>
+        <v>0.12355285642701487</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -3565,13 +3564,13 @@
         <v>25</v>
       </c>
       <c r="B3" s="19">
-        <v>2.7180501394090912</v>
+        <v>2.7337387409999998</v>
       </c>
       <c r="C3" s="8">
-        <v>0.57720057720057705</v>
+        <v>-7.0301291248206601</v>
       </c>
       <c r="D3" s="9">
-        <v>1.5688601093270364E-2</v>
+        <v>-0.19218536342754661</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -3579,13 +3578,13 @@
         <v>26</v>
       </c>
       <c r="B4" s="19">
-        <v>3.8892021594893612E-2</v>
+        <v>4.0153579000000002E-2</v>
       </c>
       <c r="C4" s="8">
-        <v>3.2437442075996201</v>
+        <v>-2.7827648114901198</v>
       </c>
       <c r="D4" s="9">
-        <v>1.2615576977027549E-3</v>
+        <v>-1.1173796669658863E-3</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -3593,13 +3592,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="19">
-        <v>30.214811484000002</v>
+        <v>30.329627769999998</v>
       </c>
       <c r="C5" s="3">
-        <v>0.38</v>
+        <v>0.71</v>
       </c>
       <c r="D5" s="9">
-        <v>0.1148162836392</v>
+        <v>0.21534035716699995</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -3607,13 +3606,13 @@
         <v>28</v>
       </c>
       <c r="B6" s="19">
-        <v>4.1106669290000006</v>
+        <v>4.1262874629999997</v>
       </c>
       <c r="C6" s="3">
-        <v>0.38</v>
+        <v>0.12</v>
       </c>
       <c r="D6" s="9">
-        <v>1.5620534330200003E-2</v>
+        <v>4.9515449555999997E-3</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -3621,13 +3620,13 @@
         <v>29</v>
       </c>
       <c r="B7" s="19">
-        <v>0.45796512960000002</v>
+        <v>0.44051665800000001</v>
       </c>
       <c r="C7" s="3">
-        <v>-3.81</v>
+        <v>3.2</v>
       </c>
       <c r="D7" s="9">
-        <v>-1.7448471437760002E-2</v>
+        <v>1.4096533055999999E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -3635,13 +3634,13 @@
         <v>80</v>
       </c>
       <c r="B8" s="19">
-        <v>0.29952548079899999</v>
+        <v>0.30428793599999998</v>
       </c>
       <c r="C8" s="3">
-        <v>1.59</v>
+        <v>-0.41</v>
       </c>
       <c r="D8" s="9">
-        <v>4.7624551447040999E-3</v>
+        <v>-1.2475805376E-3</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -3649,13 +3648,13 @@
         <v>30</v>
       </c>
       <c r="B9" s="19">
-        <v>0.23251932203499998</v>
+        <v>0.23321687999999999</v>
       </c>
       <c r="C9" s="3">
-        <v>0.3</v>
+        <v>0.11</v>
       </c>
       <c r="D9" s="9">
-        <v>6.9755796610499994E-4</v>
+        <v>2.5653856800000001E-4</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -3663,13 +3662,13 @@
         <v>103</v>
       </c>
       <c r="B10" s="19">
-        <v>3.3229845020400002E-2</v>
+        <v>3.3243136999999999E-2</v>
       </c>
       <c r="C10" s="3">
-        <v>0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="D10" s="9">
-        <v>1.3291938008160002E-5</v>
+        <v>-1.6621568500000001E-5</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -3677,558 +3676,459 @@
         <v>23</v>
       </c>
       <c r="B11" s="6">
-        <v>94.198657168230255</v>
+        <v>94.951833263999987</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="7">
-        <v>0.7531760924944666</v>
+        <v>0.16363088497300235</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="24"/>
-      <c r="C31" s="24"/>
+      <c r="B31" s="23"/>
+      <c r="C31" s="23"/>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="24"/>
-      <c r="C32" s="24"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="23"/>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="24"/>
-      <c r="C33" s="24"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="24"/>
-      <c r="C34" s="24"/>
+      <c r="B34" s="23"/>
+      <c r="C34" s="23"/>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="24"/>
-      <c r="C35" s="24"/>
+      <c r="B35" s="23"/>
+      <c r="C35" s="23"/>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="24"/>
-      <c r="C36" s="24"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="23"/>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B37" s="24"/>
-      <c r="C37" s="24"/>
+      <c r="B37" s="23"/>
+      <c r="C37" s="23"/>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B38" s="24"/>
-      <c r="C38" s="24"/>
+      <c r="B38" s="23"/>
+      <c r="C38" s="23"/>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B39" s="24"/>
-      <c r="C39" s="24"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="23"/>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B40" s="24"/>
-      <c r="C40" s="24"/>
+      <c r="B40" s="23"/>
+      <c r="C40" s="23"/>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B41" s="24"/>
-      <c r="C41" s="24"/>
+      <c r="B41" s="23"/>
+      <c r="C41" s="23"/>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B42" s="24"/>
-      <c r="C42" s="24"/>
+      <c r="B42" s="23"/>
+      <c r="C42" s="23"/>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B43" s="24"/>
-      <c r="C43" s="24"/>
+      <c r="B43" s="23"/>
+      <c r="C43" s="23"/>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B44" s="24"/>
-      <c r="C44" s="24"/>
+      <c r="B44" s="23"/>
+      <c r="C44" s="23"/>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B45" s="24"/>
-      <c r="C45" s="24"/>
+      <c r="B45" s="23"/>
+      <c r="C45" s="23"/>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B46" s="24"/>
-      <c r="C46" s="24"/>
+      <c r="B46" s="23"/>
+      <c r="C46" s="23"/>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B47" s="24"/>
-      <c r="C47" s="24"/>
+      <c r="B47" s="23"/>
+      <c r="C47" s="23"/>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B48" s="24"/>
-      <c r="C48" s="24"/>
+      <c r="B48" s="23"/>
+      <c r="C48" s="23"/>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B49" s="24"/>
-      <c r="C49" s="24"/>
+      <c r="B49" s="23"/>
+      <c r="C49" s="23"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B50" s="24"/>
-      <c r="C50" s="24"/>
+      <c r="B50" s="23"/>
+      <c r="C50" s="23"/>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B51" s="24"/>
-      <c r="C51" s="24"/>
+      <c r="B51" s="23"/>
+      <c r="C51" s="23"/>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B52" s="24"/>
-      <c r="C52" s="24"/>
+      <c r="B52" s="23"/>
+      <c r="C52" s="23"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B53" s="24"/>
-      <c r="C53" s="24"/>
+      <c r="B53" s="23"/>
+      <c r="C53" s="23"/>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B54" s="24"/>
-      <c r="C54" s="24"/>
+      <c r="B54" s="23"/>
+      <c r="C54" s="23"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B55" s="24"/>
-      <c r="C55" s="24"/>
+      <c r="B55" s="23"/>
+      <c r="C55" s="23"/>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B56" s="24"/>
-      <c r="C56" s="24"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="23"/>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B57" s="24"/>
-      <c r="C57" s="24"/>
+      <c r="B57" s="23"/>
+      <c r="C57" s="23"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B58" s="24"/>
-      <c r="C58" s="24"/>
+      <c r="B58" s="23"/>
+      <c r="C58" s="23"/>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B59" s="24"/>
-      <c r="C59" s="24"/>
+      <c r="B59" s="23"/>
+      <c r="C59" s="23"/>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B60" s="24"/>
-      <c r="C60" s="24"/>
+      <c r="B60" s="23"/>
+      <c r="C60" s="23"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B61" s="24"/>
-      <c r="C61" s="24"/>
+      <c r="B61" s="23"/>
+      <c r="C61" s="23"/>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B62" s="24"/>
-      <c r="C62" s="24"/>
+      <c r="B62" s="23"/>
+      <c r="C62" s="23"/>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B63" s="24"/>
-      <c r="C63" s="24"/>
+      <c r="B63" s="23"/>
+      <c r="C63" s="23"/>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B64" s="24"/>
-      <c r="C64" s="24"/>
+      <c r="B64" s="23"/>
+      <c r="C64" s="23"/>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B65" s="24"/>
-      <c r="C65" s="24"/>
+      <c r="B65" s="23"/>
+      <c r="C65" s="23"/>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B66" s="24"/>
-      <c r="C66" s="24"/>
+      <c r="B66" s="23"/>
+      <c r="C66" s="23"/>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B67" s="24"/>
-      <c r="C67" s="24"/>
+      <c r="B67" s="23"/>
+      <c r="C67" s="23"/>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B68" s="24"/>
-      <c r="C68" s="24"/>
+      <c r="B68" s="23"/>
+      <c r="C68" s="23"/>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B69" s="24"/>
-      <c r="C69" s="24"/>
+      <c r="B69" s="23"/>
+      <c r="C69" s="23"/>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B70" s="24"/>
-      <c r="C70" s="24"/>
+      <c r="B70" s="23"/>
+      <c r="C70" s="23"/>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B71" s="24"/>
-      <c r="C71" s="24"/>
+      <c r="B71" s="23"/>
+      <c r="C71" s="23"/>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B72" s="24"/>
-      <c r="C72" s="24"/>
+      <c r="B72" s="23"/>
+      <c r="C72" s="23"/>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B73" s="24"/>
-      <c r="C73" s="24"/>
+      <c r="B73" s="23"/>
+      <c r="C73" s="23"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B74" s="24"/>
-      <c r="C74" s="24"/>
+      <c r="B74" s="23"/>
+      <c r="C74" s="23"/>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B75" s="24"/>
-      <c r="C75" s="24"/>
+      <c r="B75" s="23"/>
+      <c r="C75" s="23"/>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B76" s="24"/>
-      <c r="C76" s="24"/>
+      <c r="B76" s="23"/>
+      <c r="C76" s="23"/>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B77" s="24"/>
-      <c r="C77" s="24"/>
+      <c r="B77" s="23"/>
+      <c r="C77" s="23"/>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B78" s="24"/>
-      <c r="C78" s="24"/>
+      <c r="B78" s="23"/>
+      <c r="C78" s="23"/>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B79" s="24"/>
-      <c r="C79" s="24"/>
+      <c r="B79" s="23"/>
+      <c r="C79" s="23"/>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B80" s="24"/>
-      <c r="C80" s="24"/>
+      <c r="B80" s="23"/>
+      <c r="C80" s="23"/>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B81" s="24"/>
-      <c r="C81" s="24"/>
+      <c r="B81" s="23"/>
+      <c r="C81" s="23"/>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B82" s="24"/>
-      <c r="C82" s="24"/>
+      <c r="B82" s="23"/>
+      <c r="C82" s="23"/>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B83" s="24"/>
-      <c r="C83" s="24"/>
+      <c r="B83" s="23"/>
+      <c r="C83" s="23"/>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B84" s="24"/>
-      <c r="C84" s="24"/>
+      <c r="B84" s="23"/>
+      <c r="C84" s="23"/>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B85" s="24"/>
-      <c r="C85" s="24"/>
+      <c r="B85" s="23"/>
+      <c r="C85" s="23"/>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B86" s="24"/>
-      <c r="C86" s="24"/>
+      <c r="B86" s="23"/>
+      <c r="C86" s="23"/>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B87" s="24"/>
-      <c r="C87" s="24"/>
+      <c r="B87" s="23"/>
+      <c r="C87" s="23"/>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B88" s="24"/>
-      <c r="C88" s="24"/>
+      <c r="B88" s="23"/>
+      <c r="C88" s="23"/>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B89" s="24"/>
-      <c r="C89" s="24"/>
+      <c r="B89" s="23"/>
+      <c r="C89" s="23"/>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B90" s="24"/>
-      <c r="C90" s="24"/>
+      <c r="B90" s="23"/>
+      <c r="C90" s="23"/>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B91" s="24"/>
-      <c r="C91" s="24"/>
+      <c r="B91" s="23"/>
+      <c r="C91" s="23"/>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B92" s="24"/>
-      <c r="C92" s="24"/>
+      <c r="B92" s="23"/>
+      <c r="C92" s="23"/>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B93" s="24"/>
-      <c r="C93" s="24"/>
+      <c r="B93" s="23"/>
+      <c r="C93" s="23"/>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B94" s="24"/>
-      <c r="C94" s="24"/>
+      <c r="B94" s="23"/>
+      <c r="C94" s="23"/>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B95" s="24"/>
-      <c r="C95" s="24"/>
+      <c r="B95" s="23"/>
+      <c r="C95" s="23"/>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B96" s="24"/>
-      <c r="C96" s="24"/>
+      <c r="B96" s="23"/>
+      <c r="C96" s="23"/>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B97" s="24"/>
-      <c r="C97" s="24"/>
+      <c r="B97" s="23"/>
+      <c r="C97" s="23"/>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B98" s="24"/>
-      <c r="C98" s="24"/>
+      <c r="B98" s="23"/>
+      <c r="C98" s="23"/>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B99" s="24"/>
-      <c r="C99" s="24"/>
+      <c r="B99" s="23"/>
+      <c r="C99" s="23"/>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B100" s="24"/>
-      <c r="C100" s="24"/>
+      <c r="B100" s="23"/>
+      <c r="C100" s="23"/>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B101" s="24"/>
-      <c r="C101" s="24"/>
+      <c r="B101" s="23"/>
+      <c r="C101" s="23"/>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B102" s="24"/>
-      <c r="C102" s="24"/>
+      <c r="B102" s="23"/>
+      <c r="C102" s="23"/>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B103" s="24"/>
-      <c r="C103" s="24"/>
+      <c r="B103" s="23"/>
+      <c r="C103" s="23"/>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B104" s="24"/>
-      <c r="C104" s="24"/>
+      <c r="B104" s="23"/>
+      <c r="C104" s="23"/>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B105" s="24"/>
-      <c r="C105" s="24"/>
+      <c r="B105" s="23"/>
+      <c r="C105" s="23"/>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B106" s="24"/>
-      <c r="C106" s="24"/>
+      <c r="B106" s="23"/>
+      <c r="C106" s="23"/>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B107" s="24"/>
-      <c r="C107" s="24"/>
+      <c r="B107" s="23"/>
+      <c r="C107" s="23"/>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B108" s="24"/>
-      <c r="C108" s="24"/>
+      <c r="B108" s="23"/>
+      <c r="C108" s="23"/>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B109" s="24"/>
-      <c r="C109" s="24"/>
+      <c r="B109" s="23"/>
+      <c r="C109" s="23"/>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B110" s="24"/>
-      <c r="C110" s="24"/>
+      <c r="B110" s="23"/>
+      <c r="C110" s="23"/>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B111" s="24"/>
-      <c r="C111" s="24"/>
+      <c r="B111" s="23"/>
+      <c r="C111" s="23"/>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B112" s="24"/>
-      <c r="C112" s="24"/>
+      <c r="B112" s="23"/>
+      <c r="C112" s="23"/>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B113" s="24"/>
-      <c r="C113" s="24"/>
+      <c r="B113" s="23"/>
+      <c r="C113" s="23"/>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B114" s="24"/>
-      <c r="C114" s="24"/>
+      <c r="B114" s="23"/>
+      <c r="C114" s="23"/>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B115" s="24"/>
-      <c r="C115" s="24"/>
+      <c r="B115" s="23"/>
+      <c r="C115" s="23"/>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B116" s="24"/>
-      <c r="C116" s="24"/>
+      <c r="B116" s="23"/>
+      <c r="C116" s="23"/>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B117" s="24"/>
-      <c r="C117" s="24"/>
+      <c r="B117" s="23"/>
+      <c r="C117" s="23"/>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B118" s="24"/>
-      <c r="C118" s="24"/>
+      <c r="B118" s="23"/>
+      <c r="C118" s="23"/>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B119" s="24"/>
-      <c r="C119" s="24"/>
+      <c r="B119" s="23"/>
+      <c r="C119" s="23"/>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B120" s="24"/>
-      <c r="C120" s="24"/>
+      <c r="B120" s="23"/>
+      <c r="C120" s="23"/>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B121" s="24"/>
-      <c r="C121" s="24"/>
+      <c r="B121" s="23"/>
+      <c r="C121" s="23"/>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B122" s="24"/>
-      <c r="C122" s="24"/>
+      <c r="B122" s="23"/>
+      <c r="C122" s="23"/>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B123" s="24"/>
-      <c r="C123" s="24"/>
+      <c r="B123" s="23"/>
+      <c r="C123" s="23"/>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B124" s="24"/>
-      <c r="C124" s="24"/>
+      <c r="B124" s="23"/>
+      <c r="C124" s="23"/>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B125" s="24"/>
-      <c r="C125" s="24"/>
+      <c r="B125" s="23"/>
+      <c r="C125" s="23"/>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B126" s="24"/>
-      <c r="C126" s="24"/>
+      <c r="B126" s="23"/>
+      <c r="C126" s="23"/>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B127" s="24"/>
-      <c r="C127" s="24"/>
+      <c r="B127" s="23"/>
+      <c r="C127" s="23"/>
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B128" s="24"/>
-      <c r="C128" s="24"/>
+      <c r="B128" s="23"/>
+      <c r="C128" s="23"/>
     </row>
     <row r="129" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B129" s="24"/>
-      <c r="C129" s="24"/>
+      <c r="B129" s="23"/>
+      <c r="C129" s="23"/>
     </row>
     <row r="130" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B130" s="24"/>
-      <c r="C130" s="24"/>
+      <c r="B130" s="23"/>
+      <c r="C130" s="23"/>
     </row>
     <row r="131" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B131" s="24"/>
-      <c r="C131" s="24"/>
+      <c r="B131" s="23"/>
+      <c r="C131" s="23"/>
     </row>
     <row r="132" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B132" s="24"/>
-      <c r="C132" s="24"/>
+      <c r="B132" s="23"/>
+      <c r="C132" s="23"/>
     </row>
     <row r="133" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B133" s="24"/>
-      <c r="C133" s="24"/>
+      <c r="B133" s="23"/>
+      <c r="C133" s="23"/>
     </row>
     <row r="134" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B134" s="24"/>
-      <c r="C134" s="24"/>
+      <c r="B134" s="23"/>
+      <c r="C134" s="23"/>
     </row>
     <row r="135" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B135" s="24"/>
-      <c r="C135" s="24"/>
+      <c r="B135" s="23"/>
+      <c r="C135" s="23"/>
     </row>
     <row r="136" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B136" s="24"/>
-      <c r="C136" s="24"/>
+      <c r="B136" s="23"/>
+      <c r="C136" s="23"/>
     </row>
     <row r="137" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B137" s="24"/>
-      <c r="C137" s="24"/>
+      <c r="B137" s="23"/>
+      <c r="C137" s="23"/>
     </row>
     <row r="138" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B138" s="24"/>
-      <c r="C138" s="24"/>
+      <c r="B138" s="23"/>
+      <c r="C138" s="23"/>
     </row>
     <row r="139" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B139" s="24"/>
-      <c r="C139" s="24"/>
+      <c r="B139" s="23"/>
+      <c r="C139" s="23"/>
     </row>
     <row r="140" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B140" s="24"/>
-      <c r="C140" s="24"/>
+      <c r="B140" s="23"/>
+      <c r="C140" s="23"/>
     </row>
     <row r="141" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B141" s="24"/>
-      <c r="C141" s="24"/>
+      <c r="B141" s="23"/>
+      <c r="C141" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="111">
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
     <mergeCell ref="B130:C130"/>
     <mergeCell ref="B131:C131"/>
     <mergeCell ref="B132:C132"/>
@@ -4241,6 +4141,105 @@
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="B138:C138"/>
     <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -4272,994 +4271,994 @@
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="22">
-        <v>7.1794871794871788</v>
+      <c r="B2" s="19">
+        <v>6.46</v>
       </c>
       <c r="C2" s="4">
-        <v>-10</v>
+        <v>-9.9537037037037006</v>
       </c>
       <c r="D2" s="5">
-        <v>-0.71794871794871795</v>
+        <v>-0.64300925925925911</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="22">
-        <v>6.4020779220779227</v>
+      <c r="B3" s="19">
+        <v>6.79</v>
       </c>
       <c r="C3" s="4">
-        <v>6.09756097560975</v>
+        <v>3.44827586206896</v>
       </c>
       <c r="D3" s="5">
-        <v>0.39037060500475101</v>
+        <v>0.23413793103448238</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="22">
-        <v>4.8033721727210423</v>
+      <c r="B4" s="19">
+        <v>4.79</v>
       </c>
       <c r="C4" s="4">
-        <v>-0.20632737276478599</v>
+        <v>-4.1350792556857296</v>
       </c>
       <c r="D4" s="5">
-        <v>-9.9106716080901453E-3</v>
+        <v>-0.19807029634734644</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="22">
-        <v>4.9091361702127667</v>
+      <c r="B5" s="19">
+        <v>4.9400000000000004</v>
       </c>
       <c r="C5" s="4">
-        <v>0.66666666666666596</v>
+        <v>-1.0347682119205199</v>
       </c>
       <c r="D5" s="5">
-        <v>3.272757446808508E-2</v>
+        <v>-5.1117549668873691E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="22">
-        <v>5.1348479262672813</v>
+      <c r="B6" s="19">
+        <v>5.01</v>
       </c>
       <c r="C6" s="4">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="D6" s="5">
-        <v>-0.12837119815668202</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="22">
-        <v>3.9972930765226447</v>
+      <c r="B7" s="19">
+        <v>3.98</v>
       </c>
       <c r="C7" s="4">
-        <v>-0.36726128016789</v>
+        <v>-4.8973143759873601</v>
       </c>
       <c r="D7" s="5">
-        <v>-1.4680509724899499E-2</v>
+        <v>-0.19491311216429694</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="22">
-        <v>3.4291729995529723</v>
+      <c r="B8" s="19">
+        <v>3.43</v>
       </c>
       <c r="C8" s="4">
-        <v>0</v>
+        <v>-2.97117516629711</v>
       </c>
       <c r="D8" s="5">
-        <v>0</v>
+        <v>-0.10191130820399089</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="22">
-        <v>3.4536315789473688</v>
+      <c r="B9" s="19">
+        <v>3.51</v>
       </c>
       <c r="C9" s="11">
-        <v>1.4925373134328299</v>
+        <v>1.9607843137254899</v>
       </c>
       <c r="D9" s="5">
-        <v>5.1546739984288888E-2</v>
+        <v>6.8823529411764686E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B10" s="22">
-        <v>3.2890490988191425</v>
+      <c r="B10" s="19">
+        <v>3.11</v>
       </c>
       <c r="C10" s="4">
-        <v>-5.3968253968253901</v>
+        <v>1.20805369127516</v>
       </c>
       <c r="D10" s="5">
-        <v>-0.1775042370791281</v>
+        <v>3.7570469798657476E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="22">
-        <v>3.10568306010929</v>
+      <c r="B11" s="19">
+        <v>3.1</v>
       </c>
       <c r="C11" s="4">
-        <v>-0.163487738419618</v>
+        <v>-5.3493449781659299</v>
       </c>
       <c r="D11" s="5">
-        <v>-5.0774109974538635E-3</v>
+        <v>-0.16582969432314382</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="22">
-        <v>2.9350447518307563</v>
+      <c r="B12" s="19">
+        <v>3.06</v>
       </c>
       <c r="C12" s="4">
-        <v>4.0972222222222197</v>
+        <v>4.6697798532354904</v>
       </c>
       <c r="D12" s="5">
-        <v>0.12025530580417675</v>
+        <v>0.14289526350900603</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="22">
-        <v>2.465581395348837</v>
+      <c r="B13" s="19">
+        <v>2.4300000000000002</v>
       </c>
       <c r="C13" s="12">
-        <v>-1.5820149875103999</v>
+        <v>-3.4686971235194499</v>
       </c>
       <c r="D13" s="5">
-        <v>-3.9005867203686651E-2</v>
+        <v>-8.4289340101522642E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="22">
-        <v>2.0793160054719566</v>
+      <c r="B14" s="19">
+        <v>1.87</v>
       </c>
       <c r="C14" s="4">
-        <v>-9.9606077658975796</v>
+        <v>-10</v>
       </c>
       <c r="D14" s="5">
-        <v>-0.20711251151859106</v>
+        <v>-0.18700000000000003</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="22">
-        <v>2.2454999999999998</v>
+      <c r="B15" s="19">
+        <v>2.2200000000000002</v>
       </c>
       <c r="C15" s="4">
-        <v>-1.25361620057859</v>
+        <v>-2.9296875</v>
       </c>
       <c r="D15" s="5">
-        <v>-2.8149951783992235E-2</v>
+        <v>-6.5039062500000008E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="22">
-        <v>1.9123886639676113</v>
+      <c r="B16" s="19">
+        <v>1.97</v>
       </c>
       <c r="C16" s="4">
-        <v>3.16831683168316</v>
+        <v>4.4145873320537401</v>
       </c>
       <c r="D16" s="5">
-        <v>6.0590531927686542E-2</v>
+        <v>8.6967370441458677E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="22">
-        <v>1.9247844827586207</v>
+      <c r="B17" s="19">
+        <v>1.91</v>
       </c>
       <c r="C17" s="11">
-        <v>-0.64608758076094697</v>
+        <v>-3.4682080924855399</v>
       </c>
       <c r="D17" s="5">
-        <v>-1.2435793499517279E-2</v>
+        <v>-6.6242774566473803E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="22">
-        <v>1.6192170818505338</v>
+      <c r="B18" s="19">
+        <v>1.59</v>
       </c>
       <c r="C18" s="4">
-        <v>-1.6252390057361299</v>
+        <v>-3.79008746355685</v>
       </c>
       <c r="D18" s="5">
-        <v>-2.6316147601777192E-2</v>
+        <v>-6.0262390670553917E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B19" s="22">
-        <v>1.4333806146572101</v>
+      <c r="B19" s="19">
+        <v>1.39</v>
       </c>
       <c r="C19" s="4">
-        <v>-2.9264214046822699</v>
+        <v>-0.68906115417743297</v>
       </c>
       <c r="D19" s="5">
-        <v>-4.1946757117894883E-2</v>
+        <v>-9.5779500430663179E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="22">
-        <v>1.4961617195496419</v>
+      <c r="B20" s="19">
+        <v>1.48</v>
       </c>
       <c r="C20" s="4">
-        <v>-1.3705583756345101</v>
+        <v>-1.54400411734431</v>
       </c>
       <c r="D20" s="5">
-        <v>-2.0505769760324925E-2</v>
+        <v>-2.2851260936695789E-2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="22">
-        <v>1.4666063348416289</v>
+      <c r="B21" s="19">
+        <v>1.49</v>
       </c>
       <c r="C21" s="4">
-        <v>1.5564202334630299</v>
+        <v>-4.2145593869731801</v>
       </c>
       <c r="D21" s="5">
-        <v>2.2826557740725666E-2</v>
+        <v>-6.2796934865900378E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="22">
-        <v>1.3679532163742689</v>
+      <c r="B22" s="19">
+        <v>1.35</v>
       </c>
       <c r="C22" s="4">
-        <v>-1.15008625646923</v>
+        <v>-3.2577079697498501</v>
       </c>
       <c r="D22" s="5">
-        <v>-1.5732641936449257E-2</v>
+        <v>-4.3979057591622982E-2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="22">
-        <v>1.1897560975609756</v>
+      <c r="B23" s="19">
+        <v>1.17</v>
       </c>
       <c r="C23" s="4">
-        <v>-1.6438356164383501</v>
+        <v>-4.7353760445682402</v>
       </c>
       <c r="D23" s="5">
-        <v>-1.955763448045432E-2</v>
+        <v>-5.5403899721448407E-2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B24" s="22">
-        <v>1.2188989169675091</v>
+      <c r="B24" s="19">
+        <v>1.1499999999999999</v>
       </c>
       <c r="C24" s="4">
-        <v>-5.6696795398520896</v>
+        <v>-4.4425087108013903</v>
       </c>
       <c r="D24" s="5">
-        <v>-6.9107662506785572E-2</v>
+        <v>-5.108885017421598E-2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="22">
-        <v>1.1196700847079804</v>
+      <c r="B25" s="19">
+        <v>1.08</v>
       </c>
       <c r="C25" s="11">
-        <v>-3.24588706091596</v>
+        <v>-2.5735294117646998</v>
       </c>
       <c r="D25" s="5">
-        <v>-3.6343226404483106E-2</v>
+        <v>-2.7794117647058761E-2</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="22">
-        <v>1.1091505791505791</v>
+      <c r="B26" s="19">
+        <v>1.06</v>
       </c>
       <c r="C26" s="11">
-        <v>-4.1329011345218802</v>
+        <v>-4.1420118343195202</v>
       </c>
       <c r="D26" s="5">
-        <v>-4.5840096869270291E-2</v>
+        <v>-4.3905325443786919E-2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="22">
-        <v>1.0060350030175016</v>
+      <c r="B27" s="19">
+        <v>1.01</v>
       </c>
       <c r="C27" s="11">
-        <v>0.544135429262394</v>
+        <v>-0.78171978352375204</v>
       </c>
       <c r="D27" s="5">
-        <v>5.47419288219922E-3</v>
+        <v>-7.8953698135898961E-3</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="22">
-        <v>0.95097137014314914</v>
+      <c r="B28" s="19">
+        <v>1</v>
       </c>
       <c r="C28" s="11">
-        <v>4.9610894941634198</v>
+        <v>3.7998146431881299</v>
       </c>
       <c r="D28" s="5">
-        <v>4.7178540736673699E-2</v>
+        <v>3.7998146431881298E-2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B29" s="22">
-        <v>0.87737051792828691</v>
+      <c r="B29" s="19">
+        <v>0.83</v>
       </c>
       <c r="C29" s="11">
-        <v>-5.84</v>
+        <v>-2.1240441801189398</v>
       </c>
       <c r="D29" s="5">
-        <v>-5.123843824701195E-2</v>
+        <v>-1.7629566694987199E-2</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B30" s="22">
-        <v>0.84430379746835438</v>
+      <c r="B30" s="19">
+        <v>0.84</v>
       </c>
       <c r="C30" s="11">
-        <v>-0.22354694485842</v>
+        <v>-4.5556385362210596</v>
       </c>
       <c r="D30" s="5">
-        <v>-1.887415344564128E-3</v>
+        <v>-3.8267363704256901E-2</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="22">
-        <v>0.82728758169934635</v>
+      <c r="B31" s="19">
+        <v>0.84</v>
       </c>
       <c r="C31" s="11">
-        <v>1.3333333333333299</v>
+        <v>-4.6052631578947301</v>
       </c>
       <c r="D31" s="5">
-        <v>1.1030501089324589E-2</v>
+        <v>-3.8684210526315731E-2</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="22">
-        <v>0.80446626814688305</v>
+      <c r="B32" s="19">
+        <v>0.76</v>
       </c>
       <c r="C32" s="11">
-        <v>-5.1709758131776402</v>
+        <v>0</v>
       </c>
       <c r="D32" s="5">
-        <v>-4.1598756151048105E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B33" s="22">
-        <v>0.77847866419294998</v>
+      <c r="B33" s="19">
+        <v>0.76</v>
       </c>
       <c r="C33" s="11">
-        <v>-2.6095060577819198</v>
+        <v>-3.4449760765550201</v>
       </c>
       <c r="D33" s="5">
-        <v>-2.0314447900654797E-2</v>
+        <v>-2.6181818181818153E-2</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B34" s="22">
-        <v>0.80238627889634595</v>
+      <c r="B34" s="19">
+        <v>0.8</v>
       </c>
       <c r="C34" s="11">
-        <v>-0.50071530758226002</v>
+        <v>-8.8425593098490296</v>
       </c>
       <c r="D34" s="5">
-        <v>-4.0176709243736888E-3</v>
+        <v>-7.074047447879224E-2</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="22">
-        <v>0.69809782608695647</v>
+      <c r="B35" s="19">
+        <v>0.68</v>
       </c>
       <c r="C35" s="11">
-        <v>-2.1857923497267699</v>
+        <v>-5.1210428305400297</v>
       </c>
       <c r="D35" s="5">
-        <v>-1.5258968876217588E-2</v>
+        <v>-3.4823091247672203E-2</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B36" s="22">
-        <v>0.71025641025641018</v>
+      <c r="B36" s="19">
+        <v>0.74</v>
       </c>
       <c r="C36" s="11">
-        <v>4.2553191489361701</v>
+        <v>-4.7619047619047601</v>
       </c>
       <c r="D36" s="5">
-        <v>3.0223677032187667E-2</v>
+        <v>-3.5238095238095221E-2</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B37" s="22">
-        <v>0.57803432137285493</v>
+      <c r="B37" s="19">
+        <v>0.56999999999999995</v>
       </c>
       <c r="C37" s="11">
-        <v>-1.11405835543766</v>
+        <v>-4.3454935622317503</v>
       </c>
       <c r="D37" s="5">
-        <v>-6.4396396545516651E-3</v>
+        <v>-2.4769313304720975E-2</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B38" s="22">
-        <v>0.54021825396825396</v>
+      <c r="B38" s="19">
+        <v>0.53</v>
       </c>
       <c r="C38" s="11">
-        <v>-1.9073569482288799</v>
+        <v>-2.9166666666666599</v>
       </c>
       <c r="D38" s="5">
-        <v>-1.0303890402664228E-2</v>
+        <v>-1.5458333333333298E-2</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B39" s="22">
-        <v>0.56087774294670845</v>
+      <c r="B39" s="19">
+        <v>0.56000000000000005</v>
       </c>
       <c r="C39" s="11">
-        <v>-0.15408320493066199</v>
+        <v>-2.4691358024691299</v>
       </c>
       <c r="D39" s="5">
-        <v>-8.6421840207504832E-4</v>
+        <v>-1.3827160493827128E-2</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B40" s="22">
-        <v>0.56231028667790894</v>
+      <c r="B40" s="19">
+        <v>0.55000000000000004</v>
       </c>
       <c r="C40" s="11">
-        <v>-2.5575447570332401</v>
+        <v>-1.3123359580052401</v>
       </c>
       <c r="D40" s="5">
-        <v>-1.4381337255189442E-2</v>
+        <v>-7.217847769028821E-3</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B41" s="22">
-        <v>0.55555743243243239</v>
+      <c r="B41" s="19">
+        <v>0.52</v>
       </c>
       <c r="C41" s="11">
-        <v>-6.1449579831932697</v>
+        <v>-5.2042529378847204</v>
       </c>
       <c r="D41" s="5">
-        <v>-3.4138770795480312E-2</v>
+        <v>-2.7062115277000549E-2</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B42" s="22">
-        <v>0.47</v>
+      <c r="B42" s="19">
+        <v>0.46</v>
       </c>
       <c r="C42" s="11">
-        <v>-1.9580419580419499</v>
+        <v>-0.57061340941512095</v>
       </c>
       <c r="D42" s="5">
-        <v>-9.2027972027971632E-3</v>
+        <v>-2.6248216833095568E-3</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B43" s="22">
-        <v>0.48282226562499997</v>
+      <c r="B43" s="19">
+        <v>0.46</v>
       </c>
       <c r="C43" s="11">
-        <v>-4.7263681592039797</v>
+        <v>-3.7075718015665799</v>
       </c>
       <c r="D43" s="5">
-        <v>-2.2819957828047261E-2</v>
+        <v>-1.7054830287206269E-2</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B44" s="22">
-        <v>0.48245681381957767</v>
+      <c r="B44" s="19">
+        <v>0.49</v>
       </c>
       <c r="C44" s="11">
-        <v>1.4677728142948301</v>
+        <v>-2.2012578616352201</v>
       </c>
       <c r="D44" s="5">
-        <v>7.0813699539567839E-3</v>
+        <v>-1.0786163522012577E-2</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B45" s="22">
-        <v>0.42112468407750631</v>
+      <c r="B45" s="19">
+        <v>0.42</v>
       </c>
       <c r="C45" s="11">
-        <v>-1.0869565217391299</v>
+        <v>-3.2967032967032899</v>
       </c>
       <c r="D45" s="5">
-        <v>-4.5774422182337619E-3</v>
+        <v>-1.3846153846153817E-2</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B46" s="22">
-        <v>0.37095442820292346</v>
+      <c r="B46" s="19">
+        <v>0.36</v>
       </c>
       <c r="C46" s="11">
-        <v>-3.5775127768313402</v>
+        <v>-3.7102473498233199</v>
       </c>
       <c r="D46" s="5">
-        <v>-1.3270942065181228E-2</v>
+        <v>-1.3356890459363951E-2</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B47" s="22">
-        <v>0.33774211400110682</v>
+      <c r="B47" s="19">
+        <v>0.33</v>
       </c>
       <c r="C47" s="11">
-        <v>-2.13698630136986</v>
+        <v>-3.9193729003359401</v>
       </c>
       <c r="D47" s="5">
-        <v>-7.2175027101606289E-3</v>
+        <v>-1.2933930571108603E-2</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B48" s="22">
-        <v>0.31278873239436622</v>
+      <c r="B48" s="19">
+        <v>0.3</v>
       </c>
       <c r="C48" s="11">
-        <v>-2.5</v>
+        <v>-3.22344322344322</v>
       </c>
       <c r="D48" s="5">
-        <v>-7.8197183098591555E-3</v>
+        <v>-9.6703296703296599E-3</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B49" s="22">
-        <v>0.30903426791277261</v>
+      <c r="B49" s="19">
+        <v>0.3</v>
       </c>
       <c r="C49" s="11">
-        <v>-1.6025641025641</v>
+        <v>-6.5146579804560201</v>
       </c>
       <c r="D49" s="5">
-        <v>-4.9524722421918606E-3</v>
+        <v>-1.9543973941368059E-2</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B50" s="22">
-        <v>0.28714924039320822</v>
+      <c r="B50" s="19">
+        <v>0.28000000000000003</v>
       </c>
       <c r="C50" s="11">
-        <v>-2.4193548387096699</v>
+        <v>-3.7649219467401198</v>
       </c>
       <c r="D50" s="5">
-        <v>-6.9471590417711452E-3</v>
+        <v>-1.0541781450872336E-2</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B51" s="22">
-        <v>0.26340678975580706</v>
+      <c r="B51" s="19">
+        <v>0.26</v>
       </c>
       <c r="C51" s="11">
-        <v>-1.3277006638503299</v>
+        <v>-4.0978593272171198</v>
       </c>
       <c r="D51" s="5">
-        <v>-3.4972536962146932E-3</v>
+        <v>-1.0654434250764511E-2</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B52" s="22">
-        <v>0.25154162384378209</v>
+      <c r="B52" s="19">
+        <v>0.25</v>
       </c>
       <c r="C52" s="11">
-        <v>-0.202634245187436</v>
+        <v>-3.6548223350253801</v>
       </c>
       <c r="D52" s="5">
-        <v>-5.0970947080806735E-4</v>
+        <v>-9.1370558375634507E-3</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B53" s="22">
-        <v>0.22879454926624737</v>
+      <c r="B53" s="19">
+        <v>0.23</v>
       </c>
       <c r="C53" s="11">
-        <v>-1.5135699373695199</v>
+        <v>-3.33863275039745</v>
       </c>
       <c r="D53" s="5">
-        <v>-3.4629655160340156E-3</v>
+        <v>-7.678855325914136E-3</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="23" t="s">
+      <c r="A54" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="B54" s="22">
-        <v>0.18957777777777779</v>
+      <c r="B54" s="19">
+        <v>0.19</v>
       </c>
       <c r="C54" s="11">
-        <v>-0.67950169875424604</v>
+        <v>0.91220068415051303</v>
       </c>
       <c r="D54" s="5">
-        <v>-1.2881842204605495E-3</v>
+        <v>1.7331812998859746E-3</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="23" t="s">
+      <c r="A55" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B55" s="22">
-        <v>0.18460567823343851</v>
+      <c r="B55" s="19">
+        <v>0.18</v>
       </c>
       <c r="C55" s="11">
-        <v>-0.488599348534202</v>
+        <v>-2.9459901800327302</v>
       </c>
       <c r="D55" s="5">
-        <v>-9.0198214120572578E-4</v>
+        <v>-5.3027823240589141E-3</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="23" t="s">
+      <c r="A56" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="B56" s="22">
-        <v>0.1912372093023256</v>
+      <c r="B56" s="19">
+        <v>0.19</v>
       </c>
       <c r="C56" s="11">
-        <v>-0.63985374771480796</v>
+        <v>-1.83992640294388</v>
       </c>
       <c r="D56" s="5">
-        <v>-1.2236384507461418E-3</v>
+        <v>-3.4958601655933719E-3</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="23" t="s">
+      <c r="A57" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="B57" s="22">
-        <v>0.19577946768060839</v>
+      <c r="B57" s="19">
+        <v>0.19</v>
       </c>
       <c r="C57" s="11">
-        <v>-1.88679245283018</v>
+        <v>-1.5384615384615301</v>
       </c>
       <c r="D57" s="5">
-        <v>-3.6939522203888208E-3</v>
+        <v>-2.9230769230769072E-3</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="23" t="s">
+      <c r="A58" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="B58" s="22">
-        <v>0.19430693069306934</v>
+      <c r="B58" s="19">
+        <v>0.19</v>
       </c>
       <c r="C58" s="11">
-        <v>-3.7516170763260002</v>
+        <v>-3.4946236559139701</v>
       </c>
       <c r="D58" s="5">
-        <v>-7.2896519923661149E-3</v>
+        <v>-6.6397849462365433E-3</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="23" t="s">
+      <c r="A59" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="B59" s="22">
-        <v>0.1846501614639397</v>
+      <c r="B59" s="19">
+        <v>0.18</v>
       </c>
       <c r="C59" s="11">
-        <v>-4.9689440993788798</v>
+        <v>-1.57952069716775</v>
       </c>
       <c r="D59" s="5">
-        <v>-9.1751633025560064E-3</v>
+        <v>-2.8431372549019502E-3</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="23" t="s">
+      <c r="A60" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="B60" s="22">
-        <v>0.16868882175226585</v>
+      <c r="B60" s="19">
+        <v>0.16</v>
       </c>
       <c r="C60" s="11">
-        <v>-2.5148908007941699</v>
+        <v>-1.9008825526137101</v>
       </c>
       <c r="D60" s="5">
-        <v>-4.2423396602158086E-3</v>
+        <v>-3.0414120841819364E-3</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="23" t="s">
+      <c r="A61" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="B61" s="22">
-        <v>0.16106666666666666</v>
+      <c r="B61" s="19">
+        <v>0.16</v>
       </c>
       <c r="C61" s="11">
-        <v>-0.46019328117809399</v>
+        <v>6.3337956541839997</v>
       </c>
       <c r="D61" s="5">
-        <v>-7.4121797821751672E-4</v>
+        <v>1.01340730466944E-2</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="23" t="s">
+      <c r="A62" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="B62" s="22">
-        <v>0.14398073836276085</v>
+      <c r="B62" s="19">
+        <v>0.14000000000000001</v>
       </c>
       <c r="C62" s="11">
-        <v>-2.01793721973094</v>
+        <v>-4.0045766590389</v>
       </c>
       <c r="D62" s="5">
-        <v>-2.9054409086655751E-3</v>
+        <v>-5.6064073226544612E-3</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="23" t="s">
+      <c r="A63" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B63" s="22">
-        <v>9.0039643211100098E-2</v>
+      <c r="B63" s="19">
+        <v>0.08</v>
       </c>
       <c r="C63" s="11">
-        <v>-9.9633251833740797</v>
+        <v>-9.9796334012219905</v>
       </c>
       <c r="D63" s="5">
-        <v>-8.9709424470717052E-3</v>
+        <v>-7.983706720977592E-3</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="23" t="s">
+      <c r="A64" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="B64" s="22">
-        <v>0.11467116357504216</v>
+      <c r="B64" s="19">
+        <v>0.12</v>
       </c>
       <c r="C64" s="11">
-        <v>0.81871345029239695</v>
+        <v>-2.20417633410672</v>
       </c>
       <c r="D64" s="5">
-        <v>9.3882823979566602E-4</v>
+        <v>-2.6450116009280639E-3</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B65" s="22">
-        <v>9.9375000000000005E-2</v>
+      <c r="B65" s="19">
+        <v>0.1</v>
       </c>
       <c r="C65" s="11">
-        <v>0.56109725685785505</v>
+        <v>-3.28580285182889</v>
       </c>
       <c r="D65" s="5">
-        <v>5.5759039900249354E-4</v>
+        <v>-3.28580285182889E-3</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B66" s="22">
-        <v>8.6679174484052546E-2</v>
+      <c r="B66" s="19">
+        <v>0.09</v>
       </c>
       <c r="C66" s="11">
-        <v>-1.7114914425427801</v>
+        <v>-6.9651741293532297</v>
       </c>
       <c r="D66" s="5">
-        <v>-1.4835066537612844E-3</v>
+        <v>-6.268656716417906E-3</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="B67" s="22">
-        <v>9.0245231607629414E-2</v>
+      <c r="B67" s="19">
+        <v>0.09</v>
       </c>
       <c r="C67" s="11">
-        <v>5.3333333333333302E-2</v>
+        <v>-4.2110874200426398</v>
       </c>
       <c r="D67" s="5">
-        <v>4.8130790190735661E-5</v>
+        <v>-3.7899786780383761E-3</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="B68" s="22">
-        <v>1.9012552301255231E-2</v>
+      <c r="B68" s="19">
+        <v>0.02</v>
       </c>
       <c r="C68" s="11">
-        <v>-1.28440366972477</v>
+        <v>5.8550185873605898</v>
       </c>
       <c r="D68" s="5">
-        <v>-2.4419791946566336E-4</v>
+        <v>1.1710037174721181E-3</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="B69" s="22">
-        <v>1.9555555555555555E-2</v>
+      <c r="B69" s="19">
+        <v>0.02</v>
       </c>
       <c r="C69" s="11">
-        <v>-2.1496815286624198</v>
+        <v>-1.30187144019528</v>
       </c>
       <c r="D69" s="5">
-        <v>-4.2038216560509546E-4</v>
+        <v>-2.60374288039056E-4</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="B70" s="22">
-        <v>2.863432</v>
+      <c r="B70" s="19">
+        <v>2.87</v>
       </c>
       <c r="C70" s="3">
-        <v>0.35</v>
+        <v>0.12</v>
       </c>
       <c r="D70" s="5">
-        <v>1.0022012E-2</v>
+        <v>3.444E-3</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="B71" s="22">
-        <v>2.7733240000000001</v>
+      <c r="B71" s="19">
+        <v>2.78</v>
       </c>
       <c r="C71" s="3">
-        <v>0.34</v>
+        <v>0.12</v>
       </c>
       <c r="D71" s="5">
-        <v>9.4293016000000004E-3</v>
+        <v>3.3359999999999996E-3</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="B72" s="22">
-        <v>2.0920899999999998</v>
+      <c r="B72" s="19">
+        <v>2.08</v>
       </c>
       <c r="C72" s="3">
-        <v>-0.61</v>
+        <v>0.11</v>
       </c>
       <c r="D72" s="5">
-        <v>-1.2761748999999998E-2</v>
+        <v>2.2880000000000001E-3</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -5267,11 +5266,11 @@
         <v>23</v>
       </c>
       <c r="B73" s="18">
-        <v>96.463946166949839</v>
+        <v>95.3</v>
       </c>
       <c r="C73" s="6"/>
       <c r="D73" s="7">
-        <v>-1.1553091698610103</v>
+        <v>-2.0542931883242939</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
+++ b/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\fonlar\etki-analizi\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D41969A-0F3C-4E39-81B8-98537440F74F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A841509-28A6-45A6-B443-F463C190511A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20790" yWindow="420" windowWidth="12765" windowHeight="20415" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21000" yWindow="165" windowWidth="10680" windowHeight="20310" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TLY" sheetId="1" r:id="rId1"/>
@@ -895,10 +895,10 @@
         <v>19.695279429999999</v>
       </c>
       <c r="C2" s="4">
-        <v>3.1055900621118</v>
+        <v>-9.9899598393574305</v>
       </c>
       <c r="D2" s="5">
-        <v>0.6116546406832295</v>
+        <v>-1.967550505306225</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -909,10 +909,10 @@
         <v>21.275529670000001</v>
       </c>
       <c r="C3" s="4">
-        <v>4.4145873320537401</v>
+        <v>-10</v>
       </c>
       <c r="D3" s="5">
-        <v>0.93922683763915504</v>
+        <v>-2.1275529670000002</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -923,10 +923,10 @@
         <v>11.20146516</v>
       </c>
       <c r="C4" s="4">
-        <v>-1.0347682119205199</v>
+        <v>-9.9958176495190294</v>
       </c>
       <c r="D4" s="5">
-        <v>-0.11590920074503201</v>
+        <v>-1.1196780314680048</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -937,10 +937,10 @@
         <v>9.709507747</v>
       </c>
       <c r="C5" s="4">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="D5" s="5">
-        <v>0</v>
+        <v>-0.97095077470000002</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>0.33639089599999999</v>
       </c>
       <c r="C6" s="4">
-        <v>3.7998146431881299</v>
+        <v>-10</v>
       </c>
       <c r="D6" s="5">
-        <v>1.2782230524559752E-2</v>
+        <v>-3.3639089599999998E-2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -965,10 +965,10 @@
         <v>7.5373858990000002</v>
       </c>
       <c r="C7" s="4">
-        <v>3.44827586206896</v>
+        <v>-10</v>
       </c>
       <c r="D7" s="5">
-        <v>0.25990985858620652</v>
+        <v>-0.75373858989999998</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -993,10 +993,10 @@
         <v>1.8240000000000001</v>
       </c>
       <c r="C9" s="4">
-        <v>-9.9537037037037006</v>
+        <v>-9.9400171379605808</v>
       </c>
       <c r="D9" s="5">
-        <v>-0.18155555555555553</v>
+        <v>-0.181305912596401</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1007,10 +1007,10 @@
         <v>1.992715832</v>
       </c>
       <c r="C10" s="4">
-        <v>4.6697798532354904</v>
+        <v>-9.9426386233269604</v>
       </c>
       <c r="D10" s="5">
-        <v>9.305544245496998E-2</v>
+        <v>-0.19812853396558316</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1021,10 +1021,10 @@
         <v>0.31376696900000001</v>
       </c>
       <c r="C11" s="4">
-        <v>-9.9796334012219905</v>
+        <v>-9.9547511312217196</v>
       </c>
       <c r="D11" s="5">
-        <v>-3.1312793240325848E-2</v>
+        <v>-3.1234720895927603E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1035,10 +1035,10 @@
         <v>0.164156359</v>
       </c>
       <c r="C12" s="4">
-        <v>-3.4686971235194499</v>
+        <v>-4.2944785276073603</v>
       </c>
       <c r="D12" s="5">
-        <v>-5.6940869027072615E-3</v>
+        <v>-7.0496595889570522E-3</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1049,10 +1049,10 @@
         <v>0.104643557</v>
       </c>
       <c r="C13" s="4">
-        <v>-3.4682080924855399</v>
+        <v>-8.5329341317365195</v>
       </c>
       <c r="D13" s="5">
-        <v>-3.6292563121387185E-3</v>
+        <v>-8.9291657919161587E-3</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1063,10 +1063,10 @@
         <v>9.5998982999999996E-2</v>
       </c>
       <c r="C14" s="4">
-        <v>-4.1350792556857296</v>
+        <v>-6.2544931703810196</v>
       </c>
       <c r="D14" s="5">
-        <v>-3.9696340317022698E-3</v>
+        <v>-6.0042498353702354E-3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1077,10 +1077,10 @@
         <v>8.5617454999999995E-2</v>
       </c>
       <c r="C15" s="4">
-        <v>-3.4682080924855399</v>
+        <v>-8.5329341317365195</v>
       </c>
       <c r="D15" s="5">
-        <v>-2.9693915028901653E-3</v>
+        <v>-7.3056810404191555E-3</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1091,10 +1091,10 @@
         <v>9.0113498E-2</v>
       </c>
       <c r="C16" s="4">
-        <v>-10</v>
+        <v>-9.9616858237547898</v>
       </c>
       <c r="D16" s="5">
-        <v>-9.0113498000000004E-3</v>
+        <v>-8.9768235555555565E-3</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1105,10 +1105,10 @@
         <v>0.72555955000000005</v>
       </c>
       <c r="C17" s="4">
-        <v>7.3732718894009199</v>
+        <v>-10</v>
       </c>
       <c r="D17" s="5">
-        <v>5.3497478341013815E-2</v>
+        <v>-7.2555955000000005E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1119,10 +1119,10 @@
         <v>6.9771245999999995E-2</v>
       </c>
       <c r="C18" s="4">
-        <v>-2.9459901800327302</v>
+        <v>-9.94940978077571</v>
       </c>
       <c r="D18" s="5">
-        <v>-2.0554540556464791E-3</v>
+        <v>-6.9418271736930801E-3</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1133,10 +1133,10 @@
         <v>6.0064433E-2</v>
       </c>
       <c r="C19" s="4">
-        <v>-3.79008746355685</v>
+        <v>-8.0808080808080796</v>
       </c>
       <c r="D19" s="5">
-        <v>-2.2764945451895034E-3</v>
+        <v>-4.8536915555555549E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1147,10 +1147,10 @@
         <v>5.9247830000000001E-2</v>
       </c>
       <c r="C20" s="4">
-        <v>-2.9296875</v>
+        <v>-3.6720321931589499</v>
       </c>
       <c r="D20" s="5">
-        <v>-1.73577626953125E-3</v>
+        <v>-2.1755993913480866E-3</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1161,10 +1161,10 @@
         <v>4.8332519999999997E-2</v>
       </c>
       <c r="C21" s="4">
-        <v>1.20805369127516</v>
+        <v>-4.5092838196286404</v>
       </c>
       <c r="D21" s="5">
-        <v>5.8388279194630495E-4</v>
+        <v>-2.1794505039787766E-3</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1175,10 +1175,10 @@
         <v>3.8551935000000002E-2</v>
       </c>
       <c r="C22" s="4">
-        <v>-3.4449760765550201</v>
+        <v>-6.1645193260654096</v>
       </c>
       <c r="D22" s="5">
-        <v>-1.3281049377990416E-3</v>
+        <v>-2.3765414836471751E-3</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1189,10 +1189,10 @@
         <v>2.7197708000000001E-2</v>
       </c>
       <c r="C23" s="4">
-        <v>-0.68906115417743297</v>
+        <v>-9.9739809193408409</v>
       </c>
       <c r="D23" s="5">
-        <v>-1.8740884065460804E-4</v>
+        <v>-2.7126942064180375E-3</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1203,10 +1203,10 @@
         <v>2.0623803999999999E-2</v>
       </c>
       <c r="C24" s="4">
-        <v>1.9607843137254899</v>
+        <v>-10</v>
       </c>
       <c r="D24" s="5">
-        <v>4.0438831372549013E-4</v>
+        <v>-2.0623803999999996E-3</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1217,10 +1217,10 @@
         <v>1.9415717999999998E-2</v>
       </c>
       <c r="C25" s="4">
-        <v>-4.6734955185659404</v>
+        <v>-9.9395567494962993</v>
       </c>
       <c r="D25" s="5">
-        <v>-9.0739271062740059E-4</v>
+        <v>-1.9298363089321677E-3</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="7">
-        <v>1.3630248104850062</v>
+        <v>-7.77</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1352,10 +1352,10 @@
         <v>9.2043840410000008</v>
       </c>
       <c r="C2" s="14">
-        <v>3.7998146431881299</v>
+        <v>-10</v>
       </c>
       <c r="D2" s="5">
-        <v>0.34974953260518937</v>
+        <v>-0.9204384041</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1366,10 +1366,10 @@
         <v>10.089677829999999</v>
       </c>
       <c r="C3" s="14">
-        <v>7.3732718894009199</v>
+        <v>-10</v>
       </c>
       <c r="D3" s="5">
-        <v>0.74393937917050668</v>
+        <v>-1.0089677829999999</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1380,10 +1380,10 @@
         <v>8.5072032909999997</v>
       </c>
       <c r="C4" s="14">
-        <v>3.44827586206896</v>
+        <v>-10</v>
       </c>
       <c r="D4" s="5">
-        <v>0.29335183762068917</v>
+        <v>-0.85072032909999995</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1394,10 +1394,10 @@
         <v>6.4374680299999998</v>
       </c>
       <c r="C5" s="14">
-        <v>-1.0347682119205199</v>
+        <v>-9.9958176495190294</v>
       </c>
       <c r="D5" s="5">
-        <v>-6.6612872826986122E-2</v>
+        <v>-0.64347756552488489</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1422,10 +1422,10 @@
         <v>5.5356164379999999</v>
       </c>
       <c r="C7" s="14">
-        <v>-9.9537037037037006</v>
+        <v>-9.9400171379605808</v>
       </c>
       <c r="D7" s="5">
-        <v>-0.55099885841203688</v>
+        <v>-0.55024122262896302</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1436,10 +1436,10 @@
         <v>4.5554010829999996</v>
       </c>
       <c r="C8" s="14">
-        <v>1.9607843137254899</v>
+        <v>-10</v>
       </c>
       <c r="D8" s="5">
-        <v>8.9321589862745063E-2</v>
+        <v>-0.45554010829999997</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1450,10 +1450,10 @@
         <v>3.3715617450000002</v>
       </c>
       <c r="C9" s="14">
-        <v>4.4145873320537401</v>
+        <v>-10</v>
       </c>
       <c r="D9" s="5">
-        <v>0.14884053768714003</v>
+        <v>-0.33715617450000002</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1464,10 +1464,10 @@
         <v>3.1200110539999999</v>
       </c>
       <c r="C10" s="14">
-        <v>-5.3493449781659299</v>
+        <v>-7.3817762399077198</v>
       </c>
       <c r="D10" s="5">
-        <v>-0.16690015463537089</v>
+        <v>-0.23031223466666642</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1478,10 +1478,10 @@
         <v>2.9109179460000001</v>
       </c>
       <c r="C11" s="14">
-        <v>-3.4686971235194499</v>
+        <v>-4.2944785276073603</v>
       </c>
       <c r="D11" s="5">
-        <v>-0.10097092706091346</v>
+        <v>-0.12500874614723922</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1492,10 +1492,10 @@
         <v>2.6307913620000001</v>
       </c>
       <c r="C12" s="14">
-        <v>1.20805369127516</v>
+        <v>-4.5092838196286404</v>
       </c>
       <c r="D12" s="5">
-        <v>3.1781372158389061E-2</v>
+        <v>-0.11862984921485394</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1506,10 +1506,10 @@
         <v>2.5082043540000001</v>
       </c>
       <c r="C13" s="14">
-        <v>-1.54400411734431</v>
+        <v>-9.0956612650287507</v>
       </c>
       <c r="D13" s="5">
-        <v>-3.8726778497169254E-2</v>
+        <v>-0.22813777187454259</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1520,10 +1520,10 @@
         <v>2.5604982180000002</v>
       </c>
       <c r="C14" s="14">
-        <v>-9.9660249150622793</v>
+        <v>-10</v>
       </c>
       <c r="D14" s="5">
-        <v>-0.25517989035560568</v>
+        <v>-0.25604982180000002</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1534,10 +1534,10 @@
         <v>2.2716763439999998</v>
       </c>
       <c r="C15" s="14">
-        <v>-0.78171978352375204</v>
+        <v>-2.6060606060606002</v>
       </c>
       <c r="D15" s="5">
-        <v>-1.7758143398677085E-2</v>
+        <v>-5.9201262298181678E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1548,10 +1548,10 @@
         <v>2.075603611</v>
       </c>
       <c r="C16" s="14">
-        <v>-4.1350792556857296</v>
+        <v>-6.2544931703810196</v>
       </c>
       <c r="D16" s="5">
-        <v>-8.5827854348724933E-2</v>
+        <v>-0.12981848609417682</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1562,10 +1562,10 @@
         <v>2.0465550000000001</v>
       </c>
       <c r="C17" s="14">
-        <v>3.1055900621118</v>
+        <v>-9.9899598393574305</v>
       </c>
       <c r="D17" s="5">
-        <v>6.3557608695652149E-2</v>
+        <v>-0.20445002259036149</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1576,10 +1576,10 @@
         <v>4.3940478470000004</v>
       </c>
       <c r="C18" s="14">
-        <v>4.6697798532354904</v>
+        <v>-9.9426386233269604</v>
       </c>
       <c r="D18" s="5">
-        <v>0.20519236110073383</v>
+        <v>-0.43688429836328879</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1590,10 +1590,10 @@
         <v>2.1330773779999999</v>
       </c>
       <c r="C19" s="14">
-        <v>-2.2012578616352201</v>
+        <v>-9.9678456591639808</v>
       </c>
       <c r="D19" s="5">
-        <v>-4.6954533477987413E-2</v>
+        <v>-0.21262186082958184</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1604,10 +1604,10 @@
         <v>0.492810054</v>
       </c>
       <c r="C20" s="14">
-        <v>-2.5072886297375998</v>
+        <v>-9.9880382775119596</v>
       </c>
       <c r="D20" s="5">
-        <v>-1.2356170450145724E-2</v>
+        <v>-4.9222056828947355E-2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1618,10 +1618,10 @@
         <v>1.5181388259999999</v>
       </c>
       <c r="C21" s="14">
-        <v>-2.5735294117646998</v>
+        <v>-9.8584905660377302</v>
       </c>
       <c r="D21" s="5">
-        <v>-3.9069749198529319E-2</v>
+        <v>-0.14966557294056593</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1632,10 +1632,10 @@
         <v>1.45238589</v>
       </c>
       <c r="C22" s="14">
-        <v>-2.97117516629711</v>
+        <v>-5.6215722120658098</v>
       </c>
       <c r="D22" s="5">
-        <v>-4.315292888248326E-2</v>
+        <v>-8.1646921604204697E-2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1646,10 +1646,10 @@
         <v>1.407561286</v>
       </c>
       <c r="C23" s="14">
-        <v>-3.2577079697498501</v>
+        <v>-1.87537810042347</v>
       </c>
       <c r="D23" s="5">
-        <v>-4.5854236193135472E-2</v>
+        <v>-2.6397096107682969E-2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1660,10 +1660,10 @@
         <v>1.2175518400000001</v>
       </c>
       <c r="C24" s="14">
-        <v>-2.9459901800327302</v>
+        <v>-9.94940978077571</v>
       </c>
       <c r="D24" s="5">
-        <v>-3.586895764320782E-2</v>
+        <v>-0.12113922185497464</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1674,10 +1674,10 @@
         <v>1.394163998</v>
       </c>
       <c r="C25" s="14">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="D25" s="5">
-        <v>0</v>
+        <v>-0.13941639980000001</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1688,10 +1688,10 @@
         <v>1.2622702079999999</v>
       </c>
       <c r="C26" s="14">
-        <v>-4.8973143759873601</v>
+        <v>-6.6445182724252403</v>
       </c>
       <c r="D26" s="5">
-        <v>-6.1817340360189543E-2</v>
+        <v>-8.3871774617940084E-2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1702,10 +1702,10 @@
         <v>1.124526409</v>
       </c>
       <c r="C27" s="14">
-        <v>-3.4682080924855399</v>
+        <v>-8.5329341317365195</v>
       </c>
       <c r="D27" s="5">
-        <v>-3.9000915919075042E-2</v>
+        <v>-9.5955097773952003E-2</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1716,10 +1716,10 @@
         <v>1.0191509219999999</v>
       </c>
       <c r="C28" s="14">
-        <v>-4.5556385362210596</v>
+        <v>-5.39906103286385</v>
       </c>
       <c r="D28" s="5">
-        <v>-4.6428832144884226E-2</v>
+        <v>-5.5024580295774644E-2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1730,10 +1730,10 @@
         <v>0.93987738600000004</v>
       </c>
       <c r="C29" s="14">
-        <v>-2.9166666666666599</v>
+        <v>-9.9427753934191703</v>
       </c>
       <c r="D29" s="5">
-        <v>-2.7413090424999936E-2</v>
+        <v>-9.344989746351931E-2</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1744,10 +1744,10 @@
         <v>0.77079706599999998</v>
       </c>
       <c r="C30" s="14">
-        <v>-2.6278409090908998</v>
+        <v>-9.9927060539751995</v>
       </c>
       <c r="D30" s="5">
-        <v>-2.0255320626420385E-2</v>
+        <v>-7.7023485078045212E-2</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1758,10 +1758,10 @@
         <v>0.66756929200000004</v>
       </c>
       <c r="C31" s="15">
-        <v>-2.9296875</v>
+        <v>-3.6720321931589499</v>
       </c>
       <c r="D31" s="5">
-        <v>-1.9557694101562502E-2</v>
+        <v>-2.4513359313883275E-2</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1772,10 +1772,10 @@
         <v>0.55160513700000002</v>
       </c>
       <c r="C32" s="14">
-        <v>-0.68906115417743297</v>
+        <v>-9.9739809193408409</v>
       </c>
       <c r="D32" s="5">
-        <v>-3.8008967235142106E-3</v>
+        <v>-5.5016991114483903E-2</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1786,10 +1786,10 @@
         <v>0.626728179</v>
       </c>
       <c r="C33" s="14">
-        <v>-1.5270935960591101</v>
+        <v>-0.45022511255627801</v>
       </c>
       <c r="D33" s="5">
-        <v>-9.5707258862068774E-3</v>
+        <v>-2.8216876493246611E-3</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1800,10 +1800,10 @@
         <v>0.58247986399999996</v>
       </c>
       <c r="C34" s="15">
-        <v>-4.0978593272171198</v>
+        <v>-4.7831632653061202</v>
       </c>
       <c r="D34" s="5">
-        <v>-2.3869205436085596E-2</v>
+        <v>-2.7860962882653047E-2</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1814,10 +1814,10 @@
         <v>0.53393117899999998</v>
       </c>
       <c r="C35" s="14">
-        <v>-3.7075718015665799</v>
+        <v>-9.9783080260303603</v>
       </c>
       <c r="D35" s="5">
-        <v>-1.9795881832375982E-2</v>
+        <v>-5.3277297687635533E-2</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1828,10 +1828,10 @@
         <v>0.53758751199999999</v>
       </c>
       <c r="C36" s="15">
-        <v>-3.79008746355685</v>
+        <v>-8.0808080808080796</v>
       </c>
       <c r="D36" s="5">
-        <v>-2.0375036897959178E-2</v>
+        <v>-4.3441415111111104E-2</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1842,10 +1842,10 @@
         <v>0.48860820300000002</v>
       </c>
       <c r="C37" s="16">
-        <v>-3.4449760765550201</v>
+        <v>-6.1645193260654096</v>
       </c>
       <c r="D37" s="5">
-        <v>-1.6832435701435389E-2</v>
+        <v>-3.0120347102675908E-2</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1856,10 +1856,10 @@
         <v>0.47146307900000001</v>
       </c>
       <c r="C38" s="15">
-        <v>-3.4946236559139701</v>
+        <v>-6.4066852367687996</v>
       </c>
       <c r="D38" s="5">
-        <v>-1.647586028763437E-2</v>
+        <v>-3.0205155479108625E-2</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1870,10 +1870,10 @@
         <v>0.43446951299999997</v>
       </c>
       <c r="C39" s="15">
-        <v>-2.5641025641025599</v>
+        <v>-10</v>
       </c>
       <c r="D39" s="5">
-        <v>-1.1140243923076904E-2</v>
+        <v>-4.3446951300000002E-2</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1884,10 +1884,10 @@
         <v>0.41539203800000002</v>
       </c>
       <c r="C40" s="15">
-        <v>0</v>
+        <v>-4.2216358839050097</v>
       </c>
       <c r="D40" s="5">
-        <v>0</v>
+        <v>-1.7536339335092334E-2</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1898,10 +1898,10 @@
         <v>0.43169741099999998</v>
       </c>
       <c r="C41" s="15">
-        <v>-2.1001615508885298</v>
+        <v>-1.3201320132013199</v>
       </c>
       <c r="D41" s="5">
-        <v>-9.06634304200323E-3</v>
+        <v>-5.6989757227722763E-3</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1912,10 +1912,10 @@
         <v>0.43892069299999997</v>
       </c>
       <c r="C42" s="15">
-        <v>-9.9770642201834807</v>
+        <v>-10</v>
       </c>
       <c r="D42" s="5">
-        <v>-4.3791399416284377E-2</v>
+        <v>-4.3892069299999996E-2</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1926,10 +1926,10 @@
         <v>0.38129521100000002</v>
       </c>
       <c r="C43" s="15">
-        <v>-4.2145593869731801</v>
+        <v>-3.2</v>
       </c>
       <c r="D43" s="5">
-        <v>-1.6069913107279694E-2</v>
+        <v>-1.2201446752000002E-2</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1940,10 +1940,10 @@
         <v>0.34629819000000001</v>
       </c>
       <c r="C44" s="15">
-        <v>-3.7649219467401198</v>
+        <v>-7.4427480916030504</v>
       </c>
       <c r="D44" s="5">
-        <v>-1.30378565564738E-2</v>
+        <v>-2.5774101927480909E-2</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1954,10 +1954,10 @@
         <v>0.34007485999999998</v>
       </c>
       <c r="C45" s="15">
-        <v>-3.2967032967032899</v>
+        <v>-5.5454545454545396</v>
       </c>
       <c r="D45" s="5">
-        <v>-1.1211259120879098E-2</v>
+        <v>-1.885869678181816E-2</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1968,10 +1968,10 @@
         <v>0.32527058800000003</v>
       </c>
       <c r="C46" s="15">
-        <v>-4.6734955185659404</v>
+        <v>-9.9395567494962993</v>
       </c>
       <c r="D46" s="5">
-        <v>-1.5201506353393084E-2</v>
+        <v>-3.2330454683680301E-2</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1982,10 +1982,10 @@
         <v>0.322708785</v>
       </c>
       <c r="C47" s="15">
-        <v>-3.9193729003359401</v>
+        <v>-4.4871794871794801</v>
       </c>
       <c r="D47" s="5">
-        <v>-1.2648160666293373E-2</v>
+        <v>-1.4480522403846129E-2</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1996,10 +1996,10 @@
         <v>0.21160512500000001</v>
       </c>
       <c r="C48" s="15">
-        <v>-9.9796334012219905</v>
+        <v>-9.9547511312217196</v>
       </c>
       <c r="D48" s="5">
-        <v>-2.1117415733197545E-2</v>
+        <v>-2.1064763574660635E-2</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -2010,10 +2010,10 @@
         <v>0.30883587400000001</v>
       </c>
       <c r="C49" s="15">
-        <v>-5.2042529378847204</v>
+        <v>-8.9138134592680007</v>
       </c>
       <c r="D49" s="5">
-        <v>-1.6072600045886953E-2</v>
+        <v>-2.7529053703659968E-2</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -2024,10 +2024,10 @@
         <v>0.33685134500000002</v>
       </c>
       <c r="C50" s="15">
-        <v>-4.1420118343195202</v>
+        <v>-7.4955908289241604</v>
       </c>
       <c r="D50" s="5">
-        <v>-1.3952422573964476E-2</v>
+        <v>-2.5248998522927682E-2</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -2038,10 +2038,10 @@
         <v>0.27836336900000003</v>
       </c>
       <c r="C51" s="15">
-        <v>-4.4425087108013903</v>
+        <v>-9.1340018231540494</v>
       </c>
       <c r="D51" s="5">
-        <v>-1.2366316915505217E-2</v>
+        <v>-2.5425715199453039E-2</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -2052,10 +2052,10 @@
         <v>0.25281408900000002</v>
       </c>
       <c r="C52" s="15">
-        <v>-4.7353760445682402</v>
+        <v>-2.9239766081871301</v>
       </c>
       <c r="D52" s="5">
-        <v>-1.1971697807799431E-2</v>
+        <v>-7.3922248245613933E-3</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -2066,10 +2066,10 @@
         <v>0.23632314300000001</v>
       </c>
       <c r="C53" s="15">
-        <v>-8.8425593098490296</v>
+        <v>-9.9369085173501492</v>
       </c>
       <c r="D53" s="5">
-        <v>-2.0897014082674335E-2</v>
+        <v>-2.3483214525236575E-2</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -2080,10 +2080,10 @@
         <v>0.184144425</v>
       </c>
       <c r="C54" s="15">
-        <v>-6.9651741293532297</v>
+        <v>-9.8930481283422402</v>
       </c>
       <c r="D54" s="5">
-        <v>-1.2825979850746261E-2</v>
+        <v>-1.8217496590909082E-2</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -2094,10 +2094,10 @@
         <v>0.20247477999999999</v>
       </c>
       <c r="C55" s="15">
-        <v>-3.6548223350253801</v>
+        <v>-4.4257112750263401</v>
       </c>
       <c r="D55" s="5">
-        <v>-7.4000934822335005E-3</v>
+        <v>-8.9609491675447777E-3</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -2108,10 +2108,10 @@
         <v>0.156684669</v>
       </c>
       <c r="C56" s="15">
-        <v>-5.1282051282051198</v>
+        <v>-1.54440154440154</v>
       </c>
       <c r="D56" s="5">
-        <v>-8.0351112307692173E-3</v>
+        <v>-2.4198404478764412E-3</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -2122,10 +2122,10 @@
         <v>0.17937023799999999</v>
       </c>
       <c r="C57" s="15">
-        <v>-4.7619047619047601</v>
+        <v>-10</v>
       </c>
       <c r="D57" s="5">
-        <v>-8.5414399047619004E-3</v>
+        <v>-1.7937023799999997E-2</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -2136,10 +2136,10 @@
         <v>0.15787469900000001</v>
       </c>
       <c r="C58" s="15">
-        <v>-1.73116089613034</v>
+        <v>-9.9481865284974091</v>
       </c>
       <c r="D58" s="5">
-        <v>-2.7330650539714768E-3</v>
+        <v>-1.5705669537823833E-2</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -2150,10 +2150,10 @@
         <v>0.12855961499999999</v>
       </c>
       <c r="C59" s="15">
-        <v>-5.9655596555965502</v>
+        <v>-9.9411379986919499</v>
       </c>
       <c r="D59" s="5">
-        <v>-7.6693005258302504E-3</v>
+        <v>-1.2780288737737075E-2</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -2164,10 +2164,10 @@
         <v>0.12855343299999999</v>
       </c>
       <c r="C60" s="15">
-        <v>-5.1210428305400297</v>
+        <v>-0.88321884200196199</v>
       </c>
       <c r="D60" s="5">
-        <v>-6.5832763640595801E-3</v>
+        <v>-1.1354081422963679E-3</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -2178,10 +2178,10 @@
         <v>0.121049672</v>
       </c>
       <c r="C61" s="15">
-        <v>0</v>
+        <v>-9.9879663056558297</v>
       </c>
       <c r="D61" s="5">
-        <v>0</v>
+        <v>-1.2090400452466898E-2</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -2192,10 +2192,10 @@
         <v>0.10348757</v>
       </c>
       <c r="C62" s="15">
-        <v>0.62893081761006298</v>
+        <v>-10</v>
       </c>
       <c r="D62" s="5">
-        <v>6.5086522012578623E-4</v>
+        <v>-1.0348757E-2</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -2206,10 +2206,10 @@
         <v>9.0058886000000005E-2</v>
       </c>
       <c r="C63" s="15">
-        <v>-3.6283185840707901</v>
+        <v>-9.8255280073461897</v>
       </c>
       <c r="D63" s="5">
-        <v>-3.2676232973451276E-3</v>
+        <v>-8.8487610670339775E-3</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -2220,10 +2220,10 @@
         <v>9.4563963000000001E-2</v>
       </c>
       <c r="C64" s="15">
-        <v>-3.0913978494623602</v>
+        <v>-7.4202496532593596</v>
       </c>
       <c r="D64" s="5">
-        <v>-2.9233483185483822E-3</v>
+        <v>-7.0168821366158093E-3</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -2234,10 +2234,10 @@
         <v>9.2286329E-2</v>
       </c>
       <c r="C65" s="15">
-        <v>-10</v>
+        <v>-9.9616858237547898</v>
       </c>
       <c r="D65" s="5">
-        <v>-9.2286329000000004E-3</v>
+        <v>-9.1932741532567055E-3</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -2248,10 +2248,10 @@
         <v>6.2085243999999998E-2</v>
       </c>
       <c r="C66" s="15">
-        <v>-3.28580285182889</v>
+        <v>-1.92307692307692</v>
       </c>
       <c r="D66" s="5">
-        <v>-2.0399987179169246E-3</v>
+        <v>-1.1939469999999982E-3</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -2262,10 +2262,10 @@
         <v>5.4377399999999999E-2</v>
       </c>
       <c r="C67" s="15">
-        <v>-2.1240441801189398</v>
+        <v>1.5190972222222201</v>
       </c>
       <c r="D67" s="5">
-        <v>-1.1549999999999963E-3</v>
+        <v>8.2604557291666547E-4</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -2276,10 +2276,10 @@
         <v>5.6951135999999999E-2</v>
       </c>
       <c r="C68" s="15">
-        <v>-3.8641686182669699</v>
+        <v>-6.8209500609013398</v>
       </c>
       <c r="D68" s="5">
-        <v>-2.200687925058543E-3</v>
+        <v>-3.8846085456760047E-3</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -2290,10 +2290,10 @@
         <v>4.8370750999999997E-2</v>
       </c>
       <c r="C69" s="15">
-        <v>4.1264266900790103</v>
+        <v>0.168634064080944</v>
       </c>
       <c r="D69" s="5">
-        <v>1.9959835794556595E-3</v>
+        <v>8.1569563237773849E-5</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -2304,10 +2304,10 @@
         <v>4.8470615000000002E-2</v>
       </c>
       <c r="C70" s="15">
-        <v>-4.0588760035682396</v>
+        <v>-5.6717805671780503</v>
       </c>
       <c r="D70" s="5">
-        <v>-1.9673621610169479E-3</v>
+        <v>-2.7491469223616893E-3</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -2318,10 +2318,10 @@
         <v>4.5534335000000002E-2</v>
       </c>
       <c r="C71" s="15">
-        <v>-3.22344322344322</v>
+        <v>-5.2990158970476902</v>
       </c>
       <c r="D71" s="5">
-        <v>-1.4677734358974346E-3</v>
+        <v>-2.4128716502649504E-3</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -2332,10 +2332,10 @@
         <v>4.0338416000000002E-2</v>
       </c>
       <c r="C72" s="15">
-        <v>-4.3454935622317503</v>
+        <v>-4.3746494671901202</v>
       </c>
       <c r="D72" s="5">
-        <v>-1.7529032703862623E-3</v>
+        <v>-1.7646643006169343E-3</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -2346,10 +2346,10 @@
         <v>3.6503475000000001E-2</v>
       </c>
       <c r="C73" s="15">
-        <v>2.5688073394495401</v>
+        <v>-9.6601073345259394</v>
       </c>
       <c r="D73" s="5">
-        <v>9.3770394495412798E-4</v>
+        <v>-3.5262748658318427E-3</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -2360,10 +2360,10 @@
         <v>2.4942332000000001E-2</v>
       </c>
       <c r="C74" s="15">
-        <v>1.7650303364589</v>
+        <v>-2.4390243902439002</v>
       </c>
       <c r="D74" s="5">
-        <v>4.4023972642029592E-4</v>
+        <v>-6.0834956097560917E-4</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -2374,10 +2374,10 @@
         <v>2.3940174000000002E-2</v>
       </c>
       <c r="C75" s="15">
-        <v>-5.3344623200677397</v>
+        <v>-9.9284436493738806</v>
       </c>
       <c r="D75" s="5">
-        <v>-1.2770795613886539E-3</v>
+        <v>-2.376886685152057E-3</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -2388,10 +2388,10 @@
         <v>1.8830533999999999E-2</v>
       </c>
       <c r="C76" s="15">
-        <v>-2.9754204398447599</v>
+        <v>0.844444444444444</v>
       </c>
       <c r="D76" s="5">
-        <v>-5.602875575679171E-4</v>
+        <v>1.5901339822222216E-4</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -2402,10 +2402,10 @@
         <v>1.9798237999999999E-2</v>
       </c>
       <c r="C77" s="15">
-        <v>-5.1282051282051198</v>
+        <v>-10</v>
       </c>
       <c r="D77" s="5">
-        <v>-1.0152942564102547E-3</v>
+        <v>-1.9798237999999998E-3</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -2416,10 +2416,10 @@
         <v>2.0020301489999999</v>
       </c>
       <c r="C78" s="15">
-        <v>0.62176165803108796</v>
+        <v>-9.9897013388259506</v>
       </c>
       <c r="D78" s="5">
-        <v>1.2447855848704661E-2</v>
+        <v>-0.19999683259835216</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="C79" s="6"/>
       <c r="D79" s="7">
-        <v>-0.28999999999999998</v>
+        <v>-8.7899999999999991</v>
       </c>
     </row>
   </sheetData>
@@ -2483,10 +2483,10 @@
         <v>12.783636363636365</v>
       </c>
       <c r="C3" s="8">
-        <v>3.44827586206896</v>
+        <v>-10</v>
       </c>
       <c r="D3" s="5">
-        <v>0.44081504702194296</v>
+        <v>-1.2783636363636364</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2497,10 +2497,10 @@
         <v>11.325483692647872</v>
       </c>
       <c r="C4" s="8">
-        <v>3.1055900621118</v>
+        <v>-9.9899598393574305</v>
       </c>
       <c r="D4" s="5">
-        <v>0.35172309604496482</v>
+        <v>-1.1314112725084973</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2511,10 +2511,10 @@
         <v>11.056410256410254</v>
       </c>
       <c r="C5" s="8">
-        <v>-9.9537037037037006</v>
+        <v>-9.9400171379605808</v>
       </c>
       <c r="D5" s="5">
-        <v>-1.1005223171889833</v>
+        <v>-1.0990090743304106</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2525,10 +2525,10 @@
         <v>6.10093572009764</v>
       </c>
       <c r="C6" s="8">
-        <v>4.6697798532354904</v>
+        <v>-9.9426386233269604</v>
       </c>
       <c r="D6" s="5">
-        <v>0.28490026711596722</v>
+        <v>-0.60659399129077873</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2539,10 +2539,10 @@
         <v>6.185991902834008</v>
       </c>
       <c r="C7" s="8">
-        <v>4.4145873320537401</v>
+        <v>-10</v>
       </c>
       <c r="D7" s="5">
-        <v>0.27308601490438023</v>
+        <v>-0.61859919028340082</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2553,10 +2553,10 @@
         <v>5.4177435897435906</v>
       </c>
       <c r="C8" s="8">
-        <v>7.3732718894009199</v>
+        <v>-10</v>
       </c>
       <c r="D8" s="5">
-        <v>0.3994649651423845</v>
+        <v>-0.5417743589743591</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2567,10 +2567,10 @@
         <v>2.8229684210526313</v>
       </c>
       <c r="C9" s="8">
-        <v>1.9607843137254899</v>
+        <v>-10</v>
       </c>
       <c r="D9" s="5">
-        <v>5.5352321981424132E-2</v>
+        <v>-0.28229684210526318</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2581,10 +2581,10 @@
         <v>2.6673319148936168</v>
       </c>
       <c r="C10" s="8">
-        <v>-1.0347682119205199</v>
+        <v>-9.9958176495190294</v>
       </c>
       <c r="D10" s="5">
-        <v>-2.7600702761730041E-2</v>
+        <v>-0.26662163432019004</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2595,10 +2595,10 @@
         <v>1.3113394683026585</v>
       </c>
       <c r="C11" s="8">
-        <v>3.7998146431881299</v>
+        <v>-10</v>
       </c>
       <c r="D11" s="5">
-        <v>4.9828469138469778E-2</v>
+        <v>-0.13113394683026583</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2609,10 +2609,10 @@
         <v>1.1868852459016395</v>
       </c>
       <c r="C12" s="8">
-        <v>-5.3493449781659299</v>
+        <v>-7.3817762399077198</v>
       </c>
       <c r="D12" s="5">
-        <v>-6.3490586298231705E-2</v>
+        <v>-8.7613213076937535E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2623,10 +2623,10 @@
         <v>1.231483870967742</v>
       </c>
       <c r="C13" s="8">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="D13" s="5">
-        <v>0</v>
+        <v>-0.12314838709677421</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2637,10 +2637,10 @@
         <v>0.28472795497185743</v>
       </c>
       <c r="C14" s="8">
-        <v>-4.7353760445682402</v>
+        <v>-2.9239766081871301</v>
       </c>
       <c r="D14" s="5">
-        <v>-1.3482939371926383E-2</v>
+        <v>-8.3253788003466965E-3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2651,10 +2651,10 @@
         <v>0.20598086124401913</v>
       </c>
       <c r="C15" s="8">
-        <v>-2.1001615508885298</v>
+        <v>-1.3201320132013199</v>
       </c>
       <c r="D15" s="5">
-        <v>-4.3259308500359431E-3</v>
+        <v>-2.7192192903500874E-3</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2665,10 +2665,10 @@
         <v>0.18893656716417911</v>
       </c>
       <c r="C16" s="8">
-        <v>-4.6734955185659404</v>
+        <v>-9.9395567494962993</v>
       </c>
       <c r="D16" s="5">
-        <v>-8.8299419993502389E-3</v>
+        <v>-1.8779457313833774E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2679,10 +2679,10 @@
         <v>0.18752732951587717</v>
       </c>
       <c r="C17" s="8">
-        <v>-4.8973143759873601</v>
+        <v>-6.6445182724252403</v>
       </c>
       <c r="D17" s="5">
-        <v>-9.1838028672862407E-3</v>
+        <v>-1.2460287675473549E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2693,10 +2693,10 @@
         <v>0.16901162790697674</v>
       </c>
       <c r="C18" s="8">
-        <v>-3.4686971235194499</v>
+        <v>-4.2944785276073603</v>
       </c>
       <c r="D18" s="5">
-        <v>-5.8625014756226975E-3</v>
+        <v>-7.2581680696247649E-3</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2707,10 +2707,10 @@
         <v>0.15850839030453698</v>
       </c>
       <c r="C19" s="8">
-        <v>1.20805369127516</v>
+        <v>-4.5092838196286404</v>
       </c>
       <c r="D19" s="5">
-        <v>1.9148664600547969E-3</v>
+        <v>-7.1475931967562986E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2721,10 +2721,10 @@
         <v>0.13078455039227521</v>
       </c>
       <c r="C20" s="8">
-        <v>-0.78171978352375204</v>
+        <v>-2.6060606060606002</v>
       </c>
       <c r="D20" s="5">
-        <v>-1.0223687042090061E-3</v>
+        <v>-3.4083246465865585E-3</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2735,10 +2735,10 @@
         <v>0.12966734902763563</v>
       </c>
       <c r="C21" s="8">
-        <v>-1.54400411734431</v>
+        <v>-9.0956612650287507</v>
       </c>
       <c r="D21" s="5">
-        <v>-2.0020692078379114E-3</v>
+        <v>-1.1794102838896288E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2749,10 +2749,10 @@
         <v>0.12070175438596491</v>
       </c>
       <c r="C22" s="8">
-        <v>-3.2577079697498501</v>
+        <v>-1.87537810042347</v>
       </c>
       <c r="D22" s="5">
-        <v>-3.9321106722594677E-3</v>
+        <v>-2.263614268581311E-3</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2763,10 +2763,10 @@
         <v>0.10357262103505845</v>
       </c>
       <c r="C23" s="8">
-        <v>-9.9660249150622793</v>
+        <v>-10</v>
       </c>
       <c r="D23" s="5">
-        <v>-1.032207321753696E-2</v>
+        <v>-1.0357262103505844E-2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2777,10 +2777,10 @@
         <v>6.9184372858122012E-2</v>
       </c>
       <c r="C24" s="8">
-        <v>-4.1350792556857296</v>
+        <v>-6.2544931703810196</v>
       </c>
       <c r="D24" s="5">
-        <v>-2.8608286502324713E-3</v>
+        <v>-4.3271318753821805E-3</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2791,10 +2791,10 @@
         <v>4.9667957941339241E-2</v>
       </c>
       <c r="C25" s="8">
-        <v>-3.9193729003359401</v>
+        <v>-4.4871794871794801</v>
       </c>
       <c r="D25" s="5">
-        <v>-1.9466724837031027E-3</v>
+        <v>-2.2286904204447061E-3</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2805,10 +2805,10 @@
         <v>3.8065054211843204E-2</v>
       </c>
       <c r="C26" s="8">
-        <v>-3.6283185840707901</v>
+        <v>-9.8255280073461897</v>
       </c>
       <c r="D26" s="5">
-        <v>-1.3811214360049278E-3</v>
+        <v>-3.7400925625961645E-3</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2819,10 +2819,10 @@
         <v>4.0107286544479211E-2</v>
       </c>
       <c r="C27" s="8">
-        <v>-2.97117516629711</v>
+        <v>-5.6215722120658098</v>
       </c>
       <c r="D27" s="5">
-        <v>-1.1916577376851886E-3</v>
+        <v>-2.2546600753980527E-3</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2833,10 +2833,10 @@
         <v>3.9482758620689659E-2</v>
       </c>
       <c r="C28" s="8">
-        <v>-3.4682080924855399</v>
+        <v>-8.5329341317365195</v>
       </c>
       <c r="D28" s="5">
-        <v>-1.369344229619291E-3</v>
+        <v>-3.3690377864959709E-3</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2847,10 +2847,10 @@
         <v>2.9939999999999998E-2</v>
       </c>
       <c r="C29" s="8">
-        <v>-2.9296875</v>
+        <v>-3.6720321931589499</v>
       </c>
       <c r="D29" s="5">
-        <v>-8.7714843749999989E-4</v>
+        <v>-1.0994064386317896E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -2861,10 +2861,10 @@
         <v>2.9798957557706625E-2</v>
       </c>
       <c r="C30" s="8">
-        <v>-4.5556385362210596</v>
+        <v>-5.39906103286385</v>
       </c>
       <c r="D30" s="5">
-        <v>-1.3575327938910409E-3</v>
+        <v>-1.6088639056977755E-3</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2875,10 +2875,10 @@
         <v>2.775800711743772E-2</v>
       </c>
       <c r="C31" s="8">
-        <v>-3.79008746355685</v>
+        <v>-8.0808080808080796</v>
       </c>
       <c r="D31" s="5">
-        <v>-1.0520527478912252E-3</v>
+        <v>-2.243071282217189E-3</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2889,10 +2889,10 @@
         <v>2.0293040293040292E-2</v>
       </c>
       <c r="C32" s="8">
-        <v>-4.7619047619047601</v>
+        <v>-10</v>
       </c>
       <c r="D32" s="5">
-        <v>-9.663352520495373E-4</v>
+        <v>-2.0293040293040293E-3</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -2903,10 +2903,10 @@
         <v>1.9945652173913045E-2</v>
       </c>
       <c r="C33" s="8">
-        <v>-5.1210428305400297</v>
+        <v>-0.88321884200196199</v>
       </c>
       <c r="D33" s="5">
-        <v>-1.0214253906566256E-3</v>
+        <v>-1.7616375816017395E-4</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -2917,10 +2917,10 @@
         <v>1.9643334819438255E-2</v>
       </c>
       <c r="C34" s="8">
-        <v>-2.5735294117646998</v>
+        <v>-9.8584905660377302</v>
       </c>
       <c r="D34" s="5">
-        <v>-5.0552699902965985E-4</v>
+        <v>-1.9365363100295248E-3</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2931,10 +2931,10 @@
         <v>1.9981949458483753E-2</v>
       </c>
       <c r="C35" s="8">
-        <v>-4.4425087108013903</v>
+        <v>-9.1340018231540494</v>
       </c>
       <c r="D35" s="5">
-        <v>-8.8769984528107196E-4</v>
+        <v>-1.8251516278396268E-3</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2945,10 +2945,10 @@
         <v>1.9511614055985706E-2</v>
       </c>
       <c r="C36" s="8">
-        <v>-4.0978593272171198</v>
+        <v>-4.7831632653061202</v>
       </c>
       <c r="D36" s="5">
-        <v>-7.9955849648381675E-4</v>
+        <v>-9.3327235599421378E-4</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2959,10 +2959,10 @@
         <v>1.9461966604823747E-2</v>
       </c>
       <c r="C37" s="8">
-        <v>-3.4449760765550201</v>
+        <v>-6.1645193260654096</v>
       </c>
       <c r="D37" s="5">
-        <v>-6.7046009356330543E-4</v>
+        <v>-1.199736692586756E-3</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2973,10 +2973,10 @@
         <v>1.9587194608256111E-2</v>
       </c>
       <c r="C38" s="8">
-        <v>-3.2967032967032899</v>
+        <v>-5.5454545454545396</v>
       </c>
       <c r="D38" s="5">
-        <v>-6.4573169038206822E-4</v>
+        <v>-1.086198973730565E-3</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2987,10 +2987,10 @@
         <v>2.0102367242482405E-2</v>
       </c>
       <c r="C39" s="8">
-        <v>-2.2012578616352201</v>
+        <v>-9.9678456591639808</v>
       </c>
       <c r="D39" s="5">
-        <v>-4.4250493929992715E-4</v>
+        <v>-2.0037729405689843E-3</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="7">
-        <v>0.23</v>
+        <v>-6.84</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -3055,10 +3055,10 @@
         <v>8.142475703550101</v>
       </c>
       <c r="C2" s="4">
-        <v>3.7998146431881299</v>
+        <v>-10</v>
       </c>
       <c r="D2" s="5">
-        <v>0.30939898410153244</v>
+        <v>-0.81424757035501016</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -3083,10 +3083,10 @@
         <v>7.1320325203886634</v>
       </c>
       <c r="C4" s="4">
-        <v>4.4145873320537401</v>
+        <v>-10</v>
       </c>
       <c r="D4" s="5">
-        <v>0.31484980416303104</v>
+        <v>-0.71320325203886636</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -3097,10 +3097,10 @@
         <v>4.5357012361152904</v>
       </c>
       <c r="C5" s="4">
-        <v>-10</v>
+        <v>-9.9616858237547898</v>
       </c>
       <c r="D5" s="5">
-        <v>-0.45357012361152904</v>
+        <v>-0.45183230704596766</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -3111,10 +3111,10 @@
         <v>9.0120080054025973</v>
       </c>
       <c r="C6" s="4">
-        <v>3.44827586206896</v>
+        <v>-10</v>
       </c>
       <c r="D6" s="5">
-        <v>0.3107588967380201</v>
+        <v>-0.90120080054025975</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -3125,10 +3125,10 @@
         <v>2.4815613914160055</v>
       </c>
       <c r="C7" s="4">
-        <v>-2.9166666666666599</v>
+        <v>-9.9427753934191703</v>
       </c>
       <c r="D7" s="5">
-        <v>-7.2378873916299991E-2</v>
+        <v>-0.24673607539830097</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -3139,10 +3139,10 @@
         <v>2.3103420198519116</v>
       </c>
       <c r="C8" s="4">
-        <v>4.6697798532354904</v>
+        <v>-9.9426386233269604</v>
       </c>
       <c r="D8" s="5">
-        <v>0.10788788618387846</v>
+        <v>-0.2297089579967484</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -3153,10 +3153,10 @@
         <v>4.2133333333333329</v>
       </c>
       <c r="C9" s="4">
-        <v>-9.9537037037037006</v>
+        <v>-9.9400171379605808</v>
       </c>
       <c r="D9" s="5">
-        <v>-0.4193827160493826</v>
+        <v>-0.41880605541273908</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -3167,10 +3167,10 @@
         <v>1.1190319312359234</v>
       </c>
       <c r="C10" s="4">
-        <v>-2.5072886297375998</v>
+        <v>-9.9880382775119596</v>
       </c>
       <c r="D10" s="5">
-        <v>-2.8057360375011383E-2</v>
+        <v>-0.11176933762942534</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -3181,10 +3181,10 @@
         <v>9.1340705128547377</v>
       </c>
       <c r="C11" s="4">
-        <v>1.9607843137254899</v>
+        <v>-10</v>
       </c>
       <c r="D11" s="5">
-        <v>0.17909942182068112</v>
+        <v>-0.91340705128547373</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -3195,10 +3195,10 @@
         <v>10.049098711951913</v>
       </c>
       <c r="C12" s="4">
-        <v>-1.0347682119205199</v>
+        <v>-9.9958176495190294</v>
       </c>
       <c r="D12" s="5">
-        <v>-0.10398487905579282</v>
+        <v>-1.0044895826668787</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -3209,10 +3209,10 @@
         <v>1.9973847169987202</v>
       </c>
       <c r="C13" s="4">
-        <v>-2.2012578616352201</v>
+        <v>-9.9678456591639808</v>
       </c>
       <c r="D13" s="5">
-        <v>-4.3967588110034719E-2</v>
+        <v>-0.1990962258101617</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -3223,10 +3223,10 @@
         <v>2.391</v>
       </c>
       <c r="C14" s="4">
-        <v>1.20805369127516</v>
+        <v>-4.5092838196286404</v>
       </c>
       <c r="D14" s="5">
-        <v>2.8884563758389076E-2</v>
+        <v>-0.1078169761273208</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -3237,10 +3237,10 @@
         <v>1.2620487802271294</v>
       </c>
       <c r="C15" s="4">
-        <v>-2.9459901800327302</v>
+        <v>-9.94940978077571</v>
       </c>
       <c r="D15" s="5">
-        <v>-3.7179833132714085E-2</v>
+        <v>-0.12556640477807857</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -3251,10 +3251,10 @@
         <v>1.8909569077519615</v>
       </c>
       <c r="C16" s="4">
-        <v>-0.78171978352375204</v>
+        <v>-2.6060606060606002</v>
       </c>
       <c r="D16" s="5">
-        <v>-1.4781984245806068E-2</v>
+        <v>-4.927948305050555E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -3265,10 +3265,10 @@
         <v>1.2658122062682029</v>
       </c>
       <c r="C17" s="4">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="D17" s="5">
-        <v>0</v>
+        <v>-0.12658122062682028</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -3279,10 +3279,10 @@
         <v>1.606964380508197</v>
       </c>
       <c r="C18" s="11">
-        <v>-5.3493449781659299</v>
+        <v>-7.3817762399077198</v>
       </c>
       <c r="D18" s="5">
-        <v>-8.5962068389630483E-2</v>
+        <v>-0.11862251482413436</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -3293,10 +3293,10 @@
         <v>1.2853032785581395</v>
       </c>
       <c r="C19" s="11">
-        <v>-3.4686971235194499</v>
+        <v>-4.2944785276073603</v>
       </c>
       <c r="D19" s="5">
-        <v>-4.4583277851847368E-2</v>
+        <v>-5.5197073312312724E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -3307,10 +3307,10 @@
         <v>1.0374311923900574</v>
       </c>
       <c r="C20" s="11">
-        <v>-9.9770642201834807</v>
+        <v>-10</v>
       </c>
       <c r="D20" s="5">
-        <v>-0.10350517630497126</v>
+        <v>-0.10374311923900574</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -3321,10 +3321,10 @@
         <v>1.1690539052194047</v>
       </c>
       <c r="C21" s="11">
-        <v>0</v>
+        <v>-9.9879663056558297</v>
       </c>
       <c r="D21" s="5">
-        <v>0</v>
+        <v>-0.11676471014826778</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -3335,10 +3335,10 @@
         <v>0.35488986740425527</v>
       </c>
       <c r="C22" s="11">
-        <v>-0.68906115417743297</v>
+        <v>-9.9739809193408409</v>
       </c>
       <c r="D22" s="5">
-        <v>-2.445408216394523E-3</v>
+        <v>-3.5396647659574426E-2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -3349,10 +3349,10 @@
         <v>0.26922888663105177</v>
       </c>
       <c r="C23" s="11">
-        <v>-9.9660249150622793</v>
+        <v>-10</v>
       </c>
       <c r="D23" s="5">
-        <v>-2.6831417920195399E-2</v>
+        <v>-2.6922888663105174E-2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -3363,10 +3363,10 @@
         <v>8.7351351015384632E-2</v>
       </c>
       <c r="C24" s="11">
-        <v>7.3732718894009199</v>
+        <v>-10</v>
       </c>
       <c r="D24" s="5">
-        <v>6.4406526094292803E-3</v>
+        <v>-8.7351351015384632E-3</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -3377,10 +3377,10 @@
         <v>0.819736841846324</v>
       </c>
       <c r="C25" s="11">
-        <v>3.1055900621118</v>
+        <v>-9.9899598393574305</v>
       </c>
       <c r="D25" s="5">
-        <v>2.5457665895848559E-2</v>
+        <v>-8.1891381288864709E-2</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -3391,10 +3391,10 @@
         <v>0.63076923069377988</v>
       </c>
       <c r="C26" s="11">
-        <v>-2.1001615508885298</v>
+        <v>-1.3201320132013199</v>
       </c>
       <c r="D26" s="5">
-        <v>-1.3247172857866136E-2</v>
+        <v>-8.3269865438122745E-3</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -3405,10 +3405,10 @@
         <v>0.40829875493806767</v>
       </c>
       <c r="C27" s="11">
-        <v>2.5688073394495401</v>
+        <v>-9.6601073345259394</v>
       </c>
       <c r="D27" s="5">
-        <v>1.0488408383730174E-2</v>
+        <v>-3.9442097972550362E-2</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -3419,10 +3419,10 @@
         <v>6.1546391343598066E-2</v>
       </c>
       <c r="C28" s="11">
-        <v>-5.1282051282051198</v>
+        <v>-10</v>
       </c>
       <c r="D28" s="5">
-        <v>-3.1562251971075875E-3</v>
+        <v>-6.1546391343598062E-3</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -3433,10 +3433,10 @@
         <v>5.8339222449871463E-2</v>
       </c>
       <c r="C29" s="11">
-        <v>-9.2812281926029296</v>
+        <v>-10</v>
       </c>
       <c r="D29" s="5">
-        <v>-5.4145963613628076E-3</v>
+        <v>-5.8339222449871461E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -3447,10 +3447,10 @@
         <v>5.8486238340517235E-2</v>
       </c>
       <c r="C30" s="11">
-        <v>9.7472924187725596</v>
+        <v>-9.8684210526315699</v>
       </c>
       <c r="D30" s="5">
-        <v>5.7008246757904871E-3</v>
+        <v>-5.77166825728788E-3</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -3461,10 +3461,10 @@
         <v>2.0676403161819536E-2</v>
       </c>
       <c r="C31" s="11">
-        <v>-8.8425593098490296</v>
+        <v>-9.9369085173501492</v>
       </c>
       <c r="D31" s="5">
-        <v>-1.8283232127273923E-3</v>
+        <v>-2.054595266868501E-3</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -3475,10 +3475,10 @@
         <v>2.6674678674000001</v>
       </c>
       <c r="C32" s="11">
-        <v>0.34</v>
+        <v>-0.35</v>
       </c>
       <c r="D32" s="5">
-        <v>9.0693907491600015E-3</v>
+        <v>-9.3361375358999993E-3</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -3489,10 +3489,10 @@
         <v>2.4571638431999996</v>
       </c>
       <c r="C33" s="11">
-        <v>0.71</v>
+        <v>0.83</v>
       </c>
       <c r="D33" s="5">
-        <v>1.7445863286719997E-2</v>
+        <v>2.0394459898559994E-2</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -3503,10 +3503,10 @@
         <v>2.3318555208</v>
       </c>
       <c r="C34" s="11">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="D34" s="5">
-        <v>3.9408358301520001E-2</v>
+        <v>3.9641543853599998E-2</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="C35" s="6"/>
       <c r="D35" s="7">
-        <v>-0.53</v>
+        <v>-7.61</v>
       </c>
     </row>
   </sheetData>
@@ -3553,10 +3553,10 @@
         <v>56.710761099999999</v>
       </c>
       <c r="C2" s="8">
-        <v>0.21786492374727601</v>
+        <v>-10</v>
       </c>
       <c r="D2" s="9">
-        <v>0.12355285642701487</v>
+        <v>-5.6710761100000004</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -3567,10 +3567,10 @@
         <v>2.7337387409999998</v>
       </c>
       <c r="C3" s="8">
-        <v>-7.0301291248206601</v>
+        <v>-9.8765432098765409</v>
       </c>
       <c r="D3" s="9">
-        <v>-0.19218536342754661</v>
+        <v>-0.26999888799999988</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -3581,10 +3581,10 @@
         <v>4.0153579000000002E-2</v>
       </c>
       <c r="C4" s="8">
-        <v>-2.7827648114901198</v>
+        <v>-9.9722991689750593</v>
       </c>
       <c r="D4" s="9">
-        <v>-1.1173796669658863E-3</v>
+        <v>-4.0042350249307442E-3</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -3595,10 +3595,10 @@
         <v>30.329627769999998</v>
       </c>
       <c r="C5" s="3">
-        <v>0.71</v>
+        <v>0.27</v>
       </c>
       <c r="D5" s="9">
-        <v>0.21534035716699995</v>
+        <v>8.1889994979E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -3623,10 +3623,10 @@
         <v>0.44051665800000001</v>
       </c>
       <c r="C7" s="3">
-        <v>3.2</v>
+        <v>-2.75</v>
       </c>
       <c r="D7" s="9">
-        <v>1.4096533055999999E-2</v>
+        <v>-1.2114208095E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -3637,10 +3637,10 @@
         <v>0.30428793599999998</v>
       </c>
       <c r="C8" s="3">
-        <v>-0.41</v>
+        <v>-1.38</v>
       </c>
       <c r="D8" s="9">
-        <v>-1.2475805376E-3</v>
+        <v>-4.1991735167999991E-3</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -3651,10 +3651,10 @@
         <v>0.23321687999999999</v>
       </c>
       <c r="C9" s="3">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="D9" s="9">
-        <v>2.5653856800000001E-4</v>
+        <v>2.3321687999999999E-4</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -3665,10 +3665,10 @@
         <v>3.3243136999999999E-2</v>
       </c>
       <c r="C10" s="3">
-        <v>-0.05</v>
+        <v>-0.25</v>
       </c>
       <c r="D10" s="9">
-        <v>-1.6621568500000001E-5</v>
+        <v>-8.3107842499999997E-5</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="7">
-        <v>0.16363088497300235</v>
+        <v>-5.87</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
@@ -4275,10 +4275,10 @@
         <v>6.46</v>
       </c>
       <c r="C2" s="4">
-        <v>-9.9537037037037006</v>
+        <v>-9.9400171379605808</v>
       </c>
       <c r="D2" s="5">
-        <v>-0.64300925925925911</v>
+        <v>-0.64212510711225346</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -4289,10 +4289,10 @@
         <v>6.79</v>
       </c>
       <c r="C3" s="4">
-        <v>3.44827586206896</v>
+        <v>-10</v>
       </c>
       <c r="D3" s="5">
-        <v>0.23413793103448238</v>
+        <v>-0.67900000000000005</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -4303,10 +4303,10 @@
         <v>4.79</v>
       </c>
       <c r="C4" s="4">
-        <v>-4.1350792556857296</v>
+        <v>-6.2544931703810196</v>
       </c>
       <c r="D4" s="5">
-        <v>-0.19807029634734644</v>
+        <v>-0.29959022286125081</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -4317,10 +4317,10 @@
         <v>4.9400000000000004</v>
       </c>
       <c r="C5" s="4">
-        <v>-1.0347682119205199</v>
+        <v>-9.9958176495190294</v>
       </c>
       <c r="D5" s="5">
-        <v>-5.1117549668873691E-2</v>
+        <v>-0.49379339188624011</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -4331,10 +4331,10 @@
         <v>5.01</v>
       </c>
       <c r="C6" s="4">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="D6" s="5">
-        <v>0</v>
+        <v>-0.50099999999999989</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -4345,10 +4345,10 @@
         <v>3.98</v>
       </c>
       <c r="C7" s="4">
-        <v>-4.8973143759873601</v>
+        <v>-6.6445182724252403</v>
       </c>
       <c r="D7" s="5">
-        <v>-0.19491311216429694</v>
+        <v>-0.26445182724252458</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -4359,10 +4359,10 @@
         <v>3.43</v>
       </c>
       <c r="C8" s="4">
-        <v>-2.97117516629711</v>
+        <v>-5.6215722120658098</v>
       </c>
       <c r="D8" s="5">
-        <v>-0.10191130820399089</v>
+        <v>-0.19281992687385727</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -4373,10 +4373,10 @@
         <v>3.51</v>
       </c>
       <c r="C9" s="11">
-        <v>1.9607843137254899</v>
+        <v>-10</v>
       </c>
       <c r="D9" s="5">
-        <v>6.8823529411764686E-2</v>
+        <v>-0.35099999999999992</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -4387,10 +4387,10 @@
         <v>3.11</v>
       </c>
       <c r="C10" s="4">
-        <v>1.20805369127516</v>
+        <v>-4.5092838196286404</v>
       </c>
       <c r="D10" s="5">
-        <v>3.7570469798657476E-2</v>
+        <v>-0.14023872679045071</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -4401,10 +4401,10 @@
         <v>3.1</v>
       </c>
       <c r="C11" s="4">
-        <v>-5.3493449781659299</v>
+        <v>-7.3817762399077198</v>
       </c>
       <c r="D11" s="5">
-        <v>-0.16582969432314382</v>
+        <v>-0.22883506343713933</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -4415,10 +4415,10 @@
         <v>3.06</v>
       </c>
       <c r="C12" s="4">
-        <v>4.6697798532354904</v>
+        <v>-9.9426386233269604</v>
       </c>
       <c r="D12" s="5">
-        <v>0.14289526350900603</v>
+        <v>-0.30424474187380501</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -4429,10 +4429,10 @@
         <v>2.4300000000000002</v>
       </c>
       <c r="C13" s="12">
-        <v>-3.4686971235194499</v>
+        <v>-4.2944785276073603</v>
       </c>
       <c r="D13" s="5">
-        <v>-8.4289340101522642E-2</v>
+        <v>-0.10435582822085886</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -4457,10 +4457,10 @@
         <v>2.2200000000000002</v>
       </c>
       <c r="C15" s="4">
-        <v>-2.9296875</v>
+        <v>-3.6720321931589499</v>
       </c>
       <c r="D15" s="5">
-        <v>-6.5039062500000008E-2</v>
+        <v>-8.1519114688128697E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -4471,10 +4471,10 @@
         <v>1.97</v>
       </c>
       <c r="C16" s="4">
-        <v>4.4145873320537401</v>
+        <v>-10</v>
       </c>
       <c r="D16" s="5">
-        <v>8.6967370441458677E-2</v>
+        <v>-0.19699999999999998</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -4485,10 +4485,10 @@
         <v>1.91</v>
       </c>
       <c r="C17" s="11">
-        <v>-3.4682080924855399</v>
+        <v>-8.5329341317365195</v>
       </c>
       <c r="D17" s="5">
-        <v>-6.6242774566473803E-2</v>
+        <v>-0.16297904191616752</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -4499,10 +4499,10 @@
         <v>1.59</v>
       </c>
       <c r="C18" s="4">
-        <v>-3.79008746355685</v>
+        <v>-8.0808080808080796</v>
       </c>
       <c r="D18" s="5">
-        <v>-6.0262390670553917E-2</v>
+        <v>-0.12848484848484848</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -4513,10 +4513,10 @@
         <v>1.39</v>
       </c>
       <c r="C19" s="4">
-        <v>-0.68906115417743297</v>
+        <v>-9.9739809193408409</v>
       </c>
       <c r="D19" s="5">
-        <v>-9.5779500430663179E-3</v>
+        <v>-0.13863833477883769</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -4527,10 +4527,10 @@
         <v>1.48</v>
       </c>
       <c r="C20" s="4">
-        <v>-1.54400411734431</v>
+        <v>-9.0956612650287507</v>
       </c>
       <c r="D20" s="5">
-        <v>-2.2851260936695789E-2</v>
+        <v>-0.1346157867224255</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -4541,10 +4541,10 @@
         <v>1.49</v>
       </c>
       <c r="C21" s="4">
-        <v>-4.2145593869731801</v>
+        <v>-3.2</v>
       </c>
       <c r="D21" s="5">
-        <v>-6.2796934865900378E-2</v>
+        <v>-4.768E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -4555,10 +4555,10 @@
         <v>1.35</v>
       </c>
       <c r="C22" s="4">
-        <v>-3.2577079697498501</v>
+        <v>-1.87537810042347</v>
       </c>
       <c r="D22" s="5">
-        <v>-4.3979057591622982E-2</v>
+        <v>-2.5317604355716849E-2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -4569,10 +4569,10 @@
         <v>1.17</v>
       </c>
       <c r="C23" s="4">
-        <v>-4.7353760445682402</v>
+        <v>-2.9239766081871301</v>
       </c>
       <c r="D23" s="5">
-        <v>-5.5403899721448407E-2</v>
+        <v>-3.421052631578942E-2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -4583,10 +4583,10 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="C24" s="4">
-        <v>-4.4425087108013903</v>
+        <v>-9.1340018231540494</v>
       </c>
       <c r="D24" s="5">
-        <v>-5.108885017421598E-2</v>
+        <v>-0.10504102096627156</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -4597,10 +4597,10 @@
         <v>1.08</v>
       </c>
       <c r="C25" s="11">
-        <v>-2.5735294117646998</v>
+        <v>-9.8584905660377302</v>
       </c>
       <c r="D25" s="5">
-        <v>-2.7794117647058761E-2</v>
+        <v>-0.10647169811320749</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -4611,10 +4611,10 @@
         <v>1.06</v>
       </c>
       <c r="C26" s="11">
-        <v>-4.1420118343195202</v>
+        <v>-7.4955908289241604</v>
       </c>
       <c r="D26" s="5">
-        <v>-4.3905325443786919E-2</v>
+        <v>-7.9453262786596104E-2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -4625,10 +4625,10 @@
         <v>1.01</v>
       </c>
       <c r="C27" s="11">
-        <v>-0.78171978352375204</v>
+        <v>-2.6060606060606002</v>
       </c>
       <c r="D27" s="5">
-        <v>-7.8953698135898961E-3</v>
+        <v>-2.6321212121212061E-2</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -4639,10 +4639,10 @@
         <v>1</v>
       </c>
       <c r="C28" s="11">
-        <v>3.7998146431881299</v>
+        <v>-10</v>
       </c>
       <c r="D28" s="5">
-        <v>3.7998146431881298E-2</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -4653,10 +4653,10 @@
         <v>0.83</v>
       </c>
       <c r="C29" s="11">
-        <v>-2.1240441801189398</v>
+        <v>1.5190972222222201</v>
       </c>
       <c r="D29" s="5">
-        <v>-1.7629566694987199E-2</v>
+        <v>1.2608506944444426E-2</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -4667,10 +4667,10 @@
         <v>0.84</v>
       </c>
       <c r="C30" s="11">
-        <v>-4.5556385362210596</v>
+        <v>-5.39906103286385</v>
       </c>
       <c r="D30" s="5">
-        <v>-3.8267363704256901E-2</v>
+        <v>-4.5352112676056343E-2</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -4681,10 +4681,10 @@
         <v>0.84</v>
       </c>
       <c r="C31" s="11">
-        <v>-4.6052631578947301</v>
+        <v>-7.5862068965517198</v>
       </c>
       <c r="D31" s="5">
-        <v>-3.8684210526315731E-2</v>
+        <v>-6.3724137931034444E-2</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -4695,10 +4695,10 @@
         <v>0.76</v>
       </c>
       <c r="C32" s="11">
-        <v>0</v>
+        <v>-4.2216358839050097</v>
       </c>
       <c r="D32" s="5">
-        <v>0</v>
+        <v>-3.2084432717678073E-2</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -4709,10 +4709,10 @@
         <v>0.76</v>
       </c>
       <c r="C33" s="11">
-        <v>-3.4449760765550201</v>
+        <v>-6.1645193260654096</v>
       </c>
       <c r="D33" s="5">
-        <v>-2.6181818181818153E-2</v>
+        <v>-4.685034687809711E-2</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -4723,10 +4723,10 @@
         <v>0.8</v>
       </c>
       <c r="C34" s="11">
-        <v>-8.8425593098490296</v>
+        <v>-9.9369085173501492</v>
       </c>
       <c r="D34" s="5">
-        <v>-7.074047447879224E-2</v>
+        <v>-7.9495268138801201E-2</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -4737,10 +4737,10 @@
         <v>0.68</v>
       </c>
       <c r="C35" s="11">
-        <v>-5.1210428305400297</v>
+        <v>-0.88321884200196199</v>
       </c>
       <c r="D35" s="5">
-        <v>-3.4823091247672203E-2</v>
+        <v>-6.0058881256133427E-3</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -4751,10 +4751,10 @@
         <v>0.74</v>
       </c>
       <c r="C36" s="11">
-        <v>-4.7619047619047601</v>
+        <v>-10</v>
       </c>
       <c r="D36" s="5">
-        <v>-3.5238095238095221E-2</v>
+        <v>-7.400000000000001E-2</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -4765,10 +4765,10 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="C37" s="11">
-        <v>-4.3454935622317503</v>
+        <v>-4.3746494671901202</v>
       </c>
       <c r="D37" s="5">
-        <v>-2.4769313304720975E-2</v>
+        <v>-2.4935501962983681E-2</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -4779,10 +4779,10 @@
         <v>0.53</v>
       </c>
       <c r="C38" s="11">
-        <v>-2.9166666666666599</v>
+        <v>-9.9427753934191703</v>
       </c>
       <c r="D38" s="5">
-        <v>-1.5458333333333298E-2</v>
+        <v>-5.2696709585121605E-2</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -4793,10 +4793,10 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="C39" s="11">
-        <v>-2.4691358024691299</v>
+        <v>-3.48101265822784</v>
       </c>
       <c r="D39" s="5">
-        <v>-1.3827160493827128E-2</v>
+        <v>-1.9493670886075908E-2</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -4807,10 +4807,10 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="C40" s="11">
-        <v>-1.3123359580052401</v>
+        <v>-4.8758865248226897</v>
       </c>
       <c r="D40" s="5">
-        <v>-7.217847769028821E-3</v>
+        <v>-2.6817375886524795E-2</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -4821,10 +4821,10 @@
         <v>0.52</v>
       </c>
       <c r="C41" s="11">
-        <v>-5.2042529378847204</v>
+        <v>-8.9138134592680007</v>
       </c>
       <c r="D41" s="5">
-        <v>-2.7062115277000549E-2</v>
+        <v>-4.6351829988193607E-2</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -4835,10 +4835,10 @@
         <v>0.46</v>
       </c>
       <c r="C42" s="11">
-        <v>-0.57061340941512095</v>
+        <v>-7.4605451936872296</v>
       </c>
       <c r="D42" s="5">
-        <v>-2.6248216833095568E-3</v>
+        <v>-3.4318507890961254E-2</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -4849,10 +4849,10 @@
         <v>0.46</v>
       </c>
       <c r="C43" s="11">
-        <v>-3.7075718015665799</v>
+        <v>-9.9783080260303603</v>
       </c>
       <c r="D43" s="5">
-        <v>-1.7054830287206269E-2</v>
+        <v>-4.590021691973966E-2</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -4863,10 +4863,10 @@
         <v>0.49</v>
       </c>
       <c r="C44" s="11">
-        <v>-2.2012578616352201</v>
+        <v>-9.9678456591639808</v>
       </c>
       <c r="D44" s="5">
-        <v>-1.0786163522012577E-2</v>
+        <v>-4.8842443729903505E-2</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -4877,10 +4877,10 @@
         <v>0.42</v>
       </c>
       <c r="C45" s="11">
-        <v>-3.2967032967032899</v>
+        <v>-5.5454545454545396</v>
       </c>
       <c r="D45" s="5">
-        <v>-1.3846153846153817E-2</v>
+        <v>-2.3290909090909064E-2</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -4891,10 +4891,10 @@
         <v>0.36</v>
       </c>
       <c r="C46" s="11">
-        <v>-3.7102473498233199</v>
+        <v>-4.03669724770642</v>
       </c>
       <c r="D46" s="5">
-        <v>-1.3356890459363951E-2</v>
+        <v>-1.453211009174311E-2</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -4905,10 +4905,10 @@
         <v>0.33</v>
       </c>
       <c r="C47" s="11">
-        <v>-3.9193729003359401</v>
+        <v>-4.4871794871794801</v>
       </c>
       <c r="D47" s="5">
-        <v>-1.2933930571108603E-2</v>
+        <v>-1.4807692307692286E-2</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -4919,10 +4919,10 @@
         <v>0.3</v>
       </c>
       <c r="C48" s="11">
-        <v>-3.22344322344322</v>
+        <v>-5.2990158970476902</v>
       </c>
       <c r="D48" s="5">
-        <v>-9.6703296703296599E-3</v>
+        <v>-1.5897047691143071E-2</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -4933,10 +4933,10 @@
         <v>0.3</v>
       </c>
       <c r="C49" s="11">
-        <v>-6.5146579804560201</v>
+        <v>-9.7560975609756095</v>
       </c>
       <c r="D49" s="5">
-        <v>-1.9543973941368059E-2</v>
+        <v>-2.9268292682926828E-2</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -4947,10 +4947,10 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="C50" s="11">
-        <v>-3.7649219467401198</v>
+        <v>-7.4427480916030504</v>
       </c>
       <c r="D50" s="5">
-        <v>-1.0541781450872336E-2</v>
+        <v>-2.0839694656488543E-2</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -4961,10 +4961,10 @@
         <v>0.26</v>
       </c>
       <c r="C51" s="11">
-        <v>-4.0978593272171198</v>
+        <v>-4.7831632653061202</v>
       </c>
       <c r="D51" s="5">
-        <v>-1.0654434250764511E-2</v>
+        <v>-1.2436224489795913E-2</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -4975,10 +4975,10 @@
         <v>0.25</v>
       </c>
       <c r="C52" s="11">
-        <v>-3.6548223350253801</v>
+        <v>-4.4257112750263401</v>
       </c>
       <c r="D52" s="5">
-        <v>-9.1370558375634507E-3</v>
+        <v>-1.106427818756585E-2</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -4989,10 +4989,10 @@
         <v>0.23</v>
       </c>
       <c r="C53" s="11">
-        <v>-3.33863275039745</v>
+        <v>-4.7697368421052602</v>
       </c>
       <c r="D53" s="5">
-        <v>-7.678855325914136E-3</v>
+        <v>-1.0970394736842099E-2</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -5003,10 +5003,10 @@
         <v>0.19</v>
       </c>
       <c r="C54" s="11">
-        <v>0.91220068415051303</v>
+        <v>-4.5197740112994298</v>
       </c>
       <c r="D54" s="5">
-        <v>1.7331812998859746E-3</v>
+        <v>-8.5875706214689155E-3</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -5017,10 +5017,10 @@
         <v>0.18</v>
       </c>
       <c r="C55" s="11">
-        <v>-2.9459901800327302</v>
+        <v>-9.94940978077571</v>
       </c>
       <c r="D55" s="5">
-        <v>-5.3027823240589141E-3</v>
+        <v>-1.7908937605396278E-2</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -5031,10 +5031,10 @@
         <v>0.19</v>
       </c>
       <c r="C56" s="11">
-        <v>-1.83992640294388</v>
+        <v>-3.8425492033739399</v>
       </c>
       <c r="D56" s="5">
-        <v>-3.4958601655933719E-3</v>
+        <v>-7.3008434864104852E-3</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -5045,10 +5045,10 @@
         <v>0.19</v>
       </c>
       <c r="C57" s="11">
-        <v>-1.5384615384615301</v>
+        <v>-6.25</v>
       </c>
       <c r="D57" s="5">
-        <v>-2.9230769230769072E-3</v>
+        <v>-1.1875E-2</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -5059,10 +5059,10 @@
         <v>0.19</v>
       </c>
       <c r="C58" s="11">
-        <v>-3.4946236559139701</v>
+        <v>-6.4066852367687996</v>
       </c>
       <c r="D58" s="5">
-        <v>-6.6397849462365433E-3</v>
+        <v>-1.2172701949860721E-2</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -5073,10 +5073,10 @@
         <v>0.18</v>
       </c>
       <c r="C59" s="11">
-        <v>-1.57952069716775</v>
+        <v>-9.9612617598229107</v>
       </c>
       <c r="D59" s="5">
-        <v>-2.8431372549019502E-3</v>
+        <v>-1.7930271167681238E-2</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -5087,10 +5087,10 @@
         <v>0.16</v>
       </c>
       <c r="C60" s="11">
-        <v>-1.9008825526137101</v>
+        <v>-7.6816608996539797</v>
       </c>
       <c r="D60" s="5">
-        <v>-3.0414120841819364E-3</v>
+        <v>-1.2290657439446368E-2</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -5101,10 +5101,10 @@
         <v>0.16</v>
       </c>
       <c r="C61" s="11">
-        <v>6.3337956541839997</v>
+        <v>2.0434782608695601</v>
       </c>
       <c r="D61" s="5">
-        <v>1.01340730466944E-2</v>
+        <v>3.2695652173912963E-3</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -5115,10 +5115,10 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="C62" s="11">
-        <v>-4.0045766590389</v>
+        <v>-2.0858164481525598</v>
       </c>
       <c r="D62" s="5">
-        <v>-5.6064073226544612E-3</v>
+        <v>-2.920143027413584E-3</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -5129,10 +5129,10 @@
         <v>0.08</v>
       </c>
       <c r="C63" s="11">
-        <v>-9.9796334012219905</v>
+        <v>-9.9547511312217196</v>
       </c>
       <c r="D63" s="5">
-        <v>-7.983706720977592E-3</v>
+        <v>-7.9638009049773761E-3</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -5143,10 +5143,10 @@
         <v>0.12</v>
       </c>
       <c r="C64" s="11">
-        <v>-2.20417633410672</v>
+        <v>-1.48279952550415</v>
       </c>
       <c r="D64" s="5">
-        <v>-2.6450116009280639E-3</v>
+        <v>-1.7793594306049797E-3</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -5157,10 +5157,10 @@
         <v>0.1</v>
       </c>
       <c r="C65" s="11">
-        <v>-3.28580285182889</v>
+        <v>-1.92307692307692</v>
       </c>
       <c r="D65" s="5">
-        <v>-3.28580285182889E-3</v>
+        <v>-1.9230769230769201E-3</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -5171,10 +5171,10 @@
         <v>0.09</v>
       </c>
       <c r="C66" s="11">
-        <v>-6.9651741293532297</v>
+        <v>-9.8930481283422402</v>
       </c>
       <c r="D66" s="5">
-        <v>-6.268656716417906E-3</v>
+        <v>-8.903743315508016E-3</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -5185,10 +5185,10 @@
         <v>0.09</v>
       </c>
       <c r="C67" s="11">
-        <v>-4.2110874200426398</v>
+        <v>-4.5631608235948802</v>
       </c>
       <c r="D67" s="5">
-        <v>-3.7899786780383761E-3</v>
+        <v>-4.1068447412353918E-3</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -5199,10 +5199,10 @@
         <v>0.02</v>
       </c>
       <c r="C68" s="11">
-        <v>5.8550185873605898</v>
+        <v>-9.9209833187006105</v>
       </c>
       <c r="D68" s="5">
-        <v>1.1710037174721181E-3</v>
+        <v>-1.984196663740122E-3</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -5213,10 +5213,10 @@
         <v>0.02</v>
       </c>
       <c r="C69" s="11">
-        <v>-1.30187144019528</v>
+        <v>-6.7600989282769897</v>
       </c>
       <c r="D69" s="5">
-        <v>-2.60374288039056E-4</v>
+        <v>-1.352019785655398E-3</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -5241,10 +5241,10 @@
         <v>2.78</v>
       </c>
       <c r="C71" s="3">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="D71" s="5">
-        <v>3.3359999999999996E-3</v>
+        <v>3.0579999999999995E-3</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -5255,10 +5255,10 @@
         <v>2.08</v>
       </c>
       <c r="C72" s="3">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="D72" s="5">
-        <v>2.2880000000000001E-3</v>
+        <v>1.872E-3</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="C73" s="6"/>
       <c r="D73" s="7">
-        <v>-2.0542931883242939</v>
+        <v>-6.65</v>
       </c>
     </row>
   </sheetData>
